--- a/engine/tmgh_study/TMGH_Valuation_Model_01092026.xlsx
+++ b/engine/tmgh_study/TMGH_Valuation_Model_01092026.xlsx
@@ -648,34 +648,34 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>105313.412801836</v>
+        <v>107316.3640287191</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>146162.1295971803</v>
+        <v>148389.7381835084</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>195269.2241350576</v>
+        <v>198092.5385168163</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>251308.7799017861</v>
+        <v>256281.5944982783</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>314160.8507770336</v>
+        <v>323422.1792900087</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>384566.8692004566</v>
+        <v>400492.965549311</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>463911.2435394029</v>
+        <v>488933.4032206548</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>554095.1116868096</v>
+        <v>590625.1829186812</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>657967.9423208544</v>
+        <v>707902.2030731476</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>778929.149926813</v>
+        <v>843585.6267175643</v>
       </c>
     </row>
     <row r="3">
@@ -691,31 +691,31 @@
         <v>147460.4685</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>150830.4417983096</v>
+        <v>148374.4597659598</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>158489.6057412495</v>
+        <v>151962.0039801408</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>169688.1411707072</v>
+        <v>158513.0362257171</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>183323.3402639077</v>
+        <v>167936.4917334951</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>198221.1542191824</v>
+        <v>179921.0811647089</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>213297.0670076518</v>
+        <v>194043.8298639381</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>227637.7040256884</v>
+        <v>209841.4955863682</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>240668.4586092294</v>
+        <v>226855.8650375194</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>252147.9821618951</v>
+        <v>244660.8971104994</v>
       </c>
     </row>
     <row r="4">
@@ -808,34 +808,34 @@
         <v>477897.9</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>507758.960261836</v>
+        <v>509761.9114887191</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>553613.8895471699</v>
+        <v>553385.5161011482</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>612568.339107991</v>
+        <v>608864.0517286409</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>682657.1224695422</v>
+        <v>676454.8321210443</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>762790.8709782829</v>
+        <v>756665.3509608455</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>852697.6675527343</v>
+        <v>850323.6908471152</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>952871.1601157255</v>
+        <v>958640.0826532637</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1064532.72979754</v>
+        <v>1083266.592590091</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1190238.928768585</v>
+        <v>1226360.595949168</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>1333487.489815557</v>
+        <v>1390656.881554913</v>
       </c>
     </row>
     <row r="7">
@@ -848,34 +848,34 @@
         <v>133993.1</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>144532.4350849398</v>
+        <v>146535.3863118228</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>165176.6421685679</v>
+        <v>165118.3753358257</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>191090.6019688985</v>
+        <v>188087.3794779219</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>218844.9105064454</v>
+        <v>214076.2295505907</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>246082.0339040108</v>
+        <v>241971.2489979393</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>271253.3323086904</v>
+        <v>270876.7987804168</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>293412.9494029774</v>
+        <v>300083.3472709557</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>312057.1967362739</v>
+        <v>329038.5529001899</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>327602.5015160459</v>
+        <v>357321.5343523726</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>340823.5993806744</v>
+        <v>384620.2995907791</v>
       </c>
     </row>
     <row r="8">
@@ -925,34 +925,34 @@
         <v>310574.2</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>321113.5350849398</v>
+        <v>323116.4863118228</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>341757.742168568</v>
+        <v>341699.4753358257</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>367671.7019688985</v>
+        <v>364668.4794779219</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>395426.0105064454</v>
+        <v>390657.3295505907</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>422663.1339040109</v>
+        <v>418552.3489979394</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>447834.4323086904</v>
+        <v>447457.8987804168</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>469994.0494029773</v>
+        <v>476664.4472709558</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>488638.2967362739</v>
+        <v>505619.6529001899</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>504183.6015160459</v>
+        <v>533902.6343523726</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>517404.6993806744</v>
+        <v>561201.3995907791</v>
       </c>
     </row>
     <row r="10">
@@ -968,31 +968,31 @@
         <v>100538.3467720459</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>112108.4697896208</v>
+        <v>112030.4016396486</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>127271.9596742513</v>
+        <v>126950.2153411502</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>146700.7994226427</v>
+        <v>146042.8636086932</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>170976.9964650831</v>
+        <v>170052.3607922203</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>200686.4856036993</v>
+        <v>199769.7858321657</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>236489.9080137721</v>
+        <v>236076.1879946845</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>279178.9612557671</v>
+        <v>279983.2506815201</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>329735.8269941406</v>
+        <v>332674.2302023828</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>389410.1882697217</v>
+        <v>395547.4057929487</v>
       </c>
     </row>
     <row r="11">
@@ -1008,31 +1008,31 @@
         <v>86107.07840485034</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>99747.6775889813</v>
+        <v>99655.63912567381</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>117624.6774648412</v>
+        <v>117245.3569095688</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>140530.3125404542</v>
+        <v>139754.6389617604</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>169150.7406091891</v>
+        <v>168060.6411706859</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>204176.7496403446</v>
+        <v>203096.0062345329</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>246387.2026989761</v>
+        <v>245899.4473876235</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>296715.4718054989</v>
+        <v>297663.6890083815</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>356319.5002583982</v>
+        <v>359783.7313944125</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>426672.6021651613</v>
+        <v>433908.0761711855</v>
       </c>
     </row>
     <row r="12">
@@ -1048,31 +1048,31 @@
         <v>186645.4251768963</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>211856.1473786021</v>
+        <v>211686.0407653225</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>244896.6371390925</v>
+        <v>244195.572250719</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>287231.1119630969</v>
+        <v>285797.5025704536</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>340127.7370742721</v>
+        <v>338113.0019629062</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>404863.2352440439</v>
+        <v>402865.7920666986</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>482877.1107127481</v>
+        <v>481975.635382308</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>575894.4330612661</v>
+        <v>577646.9396899015</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>686055.3272525388</v>
+        <v>692457.9615967954</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>816082.790434883</v>
+        <v>829455.4819641341</v>
       </c>
     </row>
     <row r="13">
@@ -1082,34 +1082,34 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>-5.820766091346741e-11</v>
+        <v>0</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>-1.164153218269348e-10</v>
+        <v>5.820766091346741e-11</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>-8.731149137020111e-11</v>
+        <v>0</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>-1.164153218269348e-10</v>
+        <v>0</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0</v>
+        <v>-1.746229827404022e-10</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0</v>
+        <v>-1.164153218269348e-10</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>-2.328306436538696e-10</v>
+        <v>-1.164153218269348e-10</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>0</v>
+        <v>-4.656612873077393e-10</v>
       </c>
     </row>
   </sheetData>
@@ -1203,34 +1203,34 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>35659.01649271284</v>
+        <v>37661.9677195959</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>48600.38228493357</v>
+        <v>48791.58186581906</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>58970.36115768577</v>
+        <v>59461.63430320401</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>68419.58884932718</v>
+        <v>70425.00700083998</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>78139.53747906498</v>
+        <v>82313.75145601362</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>89022.2821806889</v>
+        <v>95690.45111713794</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>101777.8005941502</v>
+        <v>111089.4266775959</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>117021.1765908854</v>
+        <v>129051.092189294</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>135833.2527301129</v>
+        <v>150152.0624430299</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>158939.9752893324</v>
+        <v>175033.1117484983</v>
       </c>
     </row>
     <row r="3">
@@ -1280,31 +1280,31 @@
         <v>-3800.334330876827</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>-4958.624150389217</v>
+        <v>-4925.166371829739</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>-6498.638521984519</v>
+        <v>-6394.205872072112</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-8326.645606453461</v>
+        <v>-8182.563543232703</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>-10404.08444676016</v>
+        <v>-10289.78450722588</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>-12732.63820226411</v>
+        <v>-12736.03930283377</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-15344.32389003118</v>
+        <v>-15559.88664107948</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>-18295.30853228359</v>
+        <v>-18817.31258007239</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>-21667.22817358862</v>
+        <v>-22581.84836608404</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>-25574.72626096334</v>
+        <v>-26945.64668167106</v>
       </c>
     </row>
     <row r="5">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>10539.33508493975</v>
+        <v>12542.28631182281</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>20644.20708362815</v>
+        <v>18582.98902400291</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>25913.95980033056</v>
+        <v>22969.00414209618</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>27754.30853754688</v>
+        <v>25988.85007266884</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>27237.12339756546</v>
+        <v>27895.0194473486</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>25171.29840467956</v>
+        <v>28905.54978247745</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>22159.61709428694</v>
+        <v>29206.54849053897</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>18644.24733329655</v>
+        <v>28955.20562923411</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>15545.30477977198</v>
+        <v>28282.98145218274</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>13221.09786462855</v>
+        <v>27298.76523840651</v>
       </c>
     </row>
     <row r="6">
@@ -1354,31 +1354,31 @@
         <v>854.9315000000061</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>-3369.973298309596</v>
+        <v>-913.991265959783</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>-7659.163942939929</v>
+        <v>-3587.544214180998</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-11198.53542945773</v>
+        <v>-6551.032245576323</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-13635.19909320051</v>
+        <v>-9423.455507778075</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-14897.81395527464</v>
+        <v>-11984.58943121376</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-15075.91278846937</v>
+        <v>-14122.74869922917</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>-14340.63701803664</v>
+        <v>-15797.66572243007</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>-13030.75458354094</v>
+        <v>-17014.3694511512</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>-11479.52355266579</v>
+        <v>-17805.03207298006</v>
       </c>
     </row>
     <row r="7">
@@ -1388,34 +1388,34 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>24854.89925771284</v>
+        <v>26857.8504845959</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>32743.19108644899</v>
+        <v>32623.9332271676</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>36210.03209729883</v>
+        <v>36356.02591193622</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>37358.90075724797</v>
+        <v>38926.70517958818</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>37562.72356223088</v>
+        <v>40966.15127672323</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>37703.15388024685</v>
+        <v>42935.81689718476</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>38340.26262790675</v>
+        <v>45183.34377728002</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>39832.36305608287</v>
+        <v>47983.8439038974</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>42914.74562117796</v>
+        <v>51571.39429315487</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>47810.33193218939</v>
+        <v>56163.65797474995</v>
       </c>
     </row>
     <row r="8">
@@ -1425,34 +1425,34 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>105313.412801836</v>
+        <v>107316.3640287191</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>146162.1295971803</v>
+        <v>148389.7381835084</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>195269.2241350576</v>
+        <v>198092.5385168163</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>251308.7799017861</v>
+        <v>256281.5944982783</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>314160.8507770336</v>
+        <v>323422.1792900087</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>384566.8692004566</v>
+        <v>400492.965549311</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>463911.2435394029</v>
+        <v>488933.4032206548</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>554095.1116868096</v>
+        <v>590625.1829186812</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>657967.9423208544</v>
+        <v>707902.2030731476</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>778929.149926813</v>
+        <v>843585.6267175643</v>
       </c>
     </row>
   </sheetData>
@@ -1549,31 +1549,31 @@
         <v>80502.49816</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>92464.74916857143</v>
+        <v>89119.68488285714</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>107311.4563147326</v>
+        <v>100929.6163912633</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>124240.2267948082</v>
+        <v>115687.6362130844</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>142859.3821936546</v>
+        <v>133317.8163964851</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>163112.8642584402</v>
+        <v>153905.7844076717</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>185226.9656137432</v>
+        <v>177697.5435292622</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>209675.5815216762</v>
+        <v>205104.3044690556</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>237347.4789805146</v>
+        <v>236713.5502808403</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>269394.5989417836</v>
+        <v>273306.7730339688</v>
       </c>
     </row>
     <row r="3">
@@ -1586,31 +1586,31 @@
         <v>0.316306164450336</v>
       </c>
       <c r="C3" s="10" t="n">
-        <v>0.3187203930952104</v>
+        <v>0.3207071365508213</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>0.320680098391633</v>
+        <v>0.3241508771430039</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.322852934271603</v>
+        <v>0.3270715528149806</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.3255212312993078</v>
+        <v>0.3297962508482591</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>0.3287600103832015</v>
+        <v>0.3325270973413976</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>0.3325394249999287</v>
+        <v>0.3353677700009381</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>0.3367725894890222</v>
+        <v>0.3383546349757671</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.3412786032261289</v>
+        <v>0.3414807667425755</v>
       </c>
       <c r="K3" s="10" t="n">
-        <v>0.3458585546147369</v>
+        <v>0.3447124252720621</v>
       </c>
     </row>
     <row r="4">
@@ -1623,31 +1623,31 @@
         <v>0.2346008002927391</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.2386987633612452</v>
+        <v>0.2402159223565862</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.2422063777257564</v>
+        <v>0.2449839703271598</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.2456616396523477</v>
+        <v>0.2491646025243419</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.2493521488481565</v>
+        <v>0.2530075011391331</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>0.2533977358183209</v>
+        <v>0.2566951308891773</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>0.2578163159053254</v>
+        <v>0.2603390639962059</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>0.2625611767908516</v>
+        <v>0.2639938839558895</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.2674875502650025</v>
+        <v>0.2676728952523631</v>
       </c>
       <c r="K4" s="10" t="n">
-        <v>0.272422481596279</v>
+        <v>0.2713611666036973</v>
       </c>
     </row>
     <row r="5">
@@ -1660,31 +1660,31 @@
         <v>23122.05950777309</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>30169.34635209502</v>
+        <v>29965.78196025593</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>39539.12828247499</v>
+        <v>38903.73735746867</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>50661.12043045783</v>
+        <v>49784.49386296726</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>63300.70955793542</v>
+        <v>62605.28389967848</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>77468.13637203586</v>
+        <v>77488.82940662616</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>93358.19935873547</v>
+        <v>94669.72995668893</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>111312.6308808015</v>
+        <v>114488.6168876659</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>131828.1223648613</v>
+        <v>137392.8702729778</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>155602.1894433076</v>
+        <v>163943.1670490099</v>
       </c>
     </row>
     <row r="6">
@@ -1697,31 +1697,31 @@
         <v>12667.78110292276</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>16528.74716796406</v>
+        <v>16417.22123943246</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>21662.12840661506</v>
+        <v>21314.01957357371</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>27755.48535484487</v>
+        <v>27275.21181077568</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>34680.28148920053</v>
+        <v>34299.28169075293</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>42442.12734088036</v>
+        <v>42453.46434277922</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>51147.74630010395</v>
+        <v>51866.28880359827</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>60984.36177427862</v>
+        <v>62724.37526690798</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>72224.09391196206</v>
+        <v>75272.8278869468</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>85249.08753654447</v>
+        <v>89818.82227223687</v>
       </c>
     </row>
     <row r="7">
@@ -1734,31 +1734,31 @@
         <v>6.147457230769553</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8.021117942258936</v>
+        <v>7.966996319048092</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>10.5122599471173</v>
+        <v>10.34332869188105</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>13.46926172404354</v>
+        <v>13.23619319789461</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>16.82974669942157</v>
+        <v>16.64485402193854</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>20.5964375679604</v>
+        <v>20.60193922083332</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>24.82112536327254</v>
+        <v>25.16982173502326</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>29.59466639873162</v>
+        <v>30.43906514859895</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>35.04911592231653</v>
+        <v>36.52861431015089</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>41.36992227250617</v>
+        <v>43.58753628204644</v>
       </c>
     </row>
     <row r="8">
@@ -1768,34 +1768,34 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>300000</v>
+        <v>183838.2</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>255000</v>
+        <v>183838.2</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>216750</v>
+        <v>183838.2</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>184237.5</v>
+        <v>183838.2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>156601.875</v>
+        <v>183838.2</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>133111.59375</v>
+        <v>183838.2</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>113144.8546875</v>
+        <v>183838.2</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>96173.12648437498</v>
+        <v>183838.2</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>92160.0606257667</v>
+        <v>183838.2</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>95259.00317929126</v>
+        <v>183838.2</v>
       </c>
     </row>
     <row r="9">
@@ -1805,34 +1805,34 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>741662.77584</v>
+        <v>625500.97584</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>941862.3081514286</v>
+        <v>757883.7724371428</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>1096822.451882296</v>
+        <v>886313.9560914795</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1211841.48911112</v>
+        <v>1009486.283902027</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>1292093.028387896</v>
+        <v>1126515.713975973</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>1342491.787807302</v>
+        <v>1236848.159496147</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1367608.505273735</v>
+        <v>1340187.644359561</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>1371621.571132343</v>
+        <v>1436437.060786415</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>1368522.628578818</v>
+        <v>1525650.186306798</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>1366198.421663675</v>
+        <v>1607993.002120178</v>
       </c>
     </row>
     <row r="10">
@@ -1842,34 +1842,34 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>15.03251932931608</v>
+        <v>12.67807393888858</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>17.18712171406984</v>
+        <v>14.72894433464028</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>17.75084970427772</v>
+        <v>15.99613223043764</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>17.50748919572586</v>
+        <v>16.6401017156651</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>16.92321344953666</v>
+        <v>16.86179397140276</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>16.23075546464174</v>
+        <v>16.82654872735997</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>15.53603823103998</v>
+        <v>16.64855944701225</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>14.88303677123294</v>
+        <v>16.3997831935505</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>14.36633371024322</v>
+        <v>16.12310684770383</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>14.00034309530868</v>
+        <v>15.8430160642927</v>
       </c>
     </row>
   </sheetData>
@@ -2040,10 +2040,10 @@
         <v>0.18</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>195.3754727204837</v>
+        <v>201.6036914169526</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>144.65633402848</v>
+        <v>189.998087394918</v>
       </c>
       <c r="D2" s="10">
         <f>B2/'Summary'!$B$2-1</f>
@@ -2055,10 +2055,10 @@
         <v>0.22</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>107.5609373179974</v>
+        <v>112.6846705623544</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>61.55781669909621</v>
+        <v>102.0012224605793</v>
       </c>
       <c r="D3" s="10">
         <f>B3/'Summary'!$B$2-1</f>
@@ -2070,10 +2070,10 @@
         <v>0.26</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>80.14561888690895</v>
+        <v>84.40119551906773</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>39.01394934194048</v>
+        <v>74.73108003622716</v>
       </c>
       <c r="D4" s="10">
         <f>B4/'Summary'!$B$2-1</f>
@@ -2085,10 +2085,10 @@
         <v>0.3</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>65.63699362659911</v>
+        <v>69.20894631831915</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>29.0830618982985</v>
+        <v>60.52657784743045</v>
       </c>
       <c r="D5" s="10">
         <f>B5/'Summary'!$B$2-1</f>
@@ -2100,10 +2100,10 @@
         <v>0.3237</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>59.68128664954667</v>
+        <v>62.9177551183162</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>25.62685477596697</v>
+        <v>54.78614785024519</v>
       </c>
       <c r="D6" s="10">
         <f>B6/'Summary'!$B$2-1</f>
@@ -2115,10 +2115,10 @@
         <v>0.3579</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>53.05126699236023</v>
+        <v>55.87736705533258</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>22.29789988459999</v>
+        <v>48.48386209848692</v>
       </c>
       <c r="D7" s="10">
         <f>B7/'Summary'!$B$2-1</f>
@@ -2130,10 +2130,10 @@
         <v>0.4</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>46.92942906943123</v>
+        <v>49.34699464482212</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>19.75271103450331</v>
+        <v>42.76571683996426</v>
       </c>
       <c r="D8" s="10">
         <f>B8/'Summary'!$B$2-1</f>
@@ -2157,7 +2157,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>14.82779888043417</v>
+        <v>46.41982156593504</v>
       </c>
     </row>
     <row r="12">
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>31.91934450936661</v>
+        <v>50.65079038861755</v>
       </c>
     </row>
     <row r="13">
@@ -2173,7 +2173,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>44.00708088071568</v>
+        <v>53.64100588478227</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>53.04552746781089</v>
+        <v>55.87125667167204</v>
       </c>
     </row>
     <row r="15">
@@ -2189,7 +2189,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>60.06333889357035</v>
+        <v>57.60028647411903</v>
       </c>
     </row>
     <row r="16">
@@ -2197,7 +2197,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>70.27885274962011</v>
+        <v>60.10808915327755</v>
       </c>
     </row>
   </sheetData>
@@ -2660,17 +2660,17 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>97667.3677495489</v>
+        <v>103490.2173712564</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>109308.4677495489</v>
+        <v>115131.3173712563</v>
       </c>
       <c r="D7" s="9">
         <f>C7/$B$3</f>
         <v/>
       </c>
       <c r="E7" s="9" t="n">
-        <v>49.17559016103478</v>
+        <v>50.72370923510034</v>
       </c>
       <c r="F7" s="10">
         <f>D7/$B$2-1</f>
@@ -2684,17 +2684,17 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>34301.73524063985</v>
+        <v>88256.20771011799</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>45942.83524063986</v>
+        <v>99897.307710118</v>
       </c>
       <c r="D8" s="9">
         <f>C8/$B$3</f>
         <v/>
       </c>
       <c r="E8" s="9" t="n">
-        <v>32.3285907191181</v>
+        <v>46.67344820088329</v>
       </c>
       <c r="F8" s="10">
         <f>D8/$B$2-1</f>
@@ -2708,17 +2708,17 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>111318.985505366</v>
+        <v>117986.9049356308</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>122960.085505366</v>
+        <v>129628.0049356308</v>
       </c>
       <c r="D9" s="9">
         <f>C9/$B$3</f>
         <v/>
       </c>
       <c r="E9" s="9" t="n">
-        <v>52.80514119062761</v>
+        <v>54.57793869098589</v>
       </c>
       <c r="F9" s="10">
         <f>D9/$B$2-1</f>
@@ -2732,17 +2732,17 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>41154.78223798759</v>
+        <v>101232.7379730227</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>52795.88223798759</v>
+        <v>112873.8379730227</v>
       </c>
       <c r="D10" s="9">
         <f>C10/$B$3</f>
         <v/>
       </c>
       <c r="E10" s="9" t="n">
-        <v>34.15060802358537</v>
+        <v>50.12351394537711</v>
       </c>
       <c r="F10" s="10">
         <f>D10/$B$2-1</f>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.230888996245817</v>
+        <v>0.237271115555085</v>
       </c>
     </row>
     <row r="16">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.1943462659268372</v>
+        <v>0.2243557037726325</v>
       </c>
     </row>
     <row r="17">
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>22.29527116133718</v>
+        <v>48.47845266881705</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>59.67042377781557</v>
+        <v>62.90625088776715</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
@@ -3119,30 +3119,30 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Normalised annual contracted sales, EGP mn</t>
+          <t>Annual contracted sales, EGP mn</t>
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>300000</v>
+        <v>382200</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>below the 2025 figure and far below 2024's launch year</t>
+          <t>FY2025 as reported, held flat in nominal terms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Sales fade toward the delivery rate, a year</t>
+          <t>Share of contracted sales that enters the order book</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.85</v>
+        <v>0.481</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>TMG currently sells about ten times what it delivers; that is not a steady state and is not extrapolated</t>
+          <t>measured on the company's own two disclosed series; FY2025 was 48.1%</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>88580.39593351606</v>
+        <v>94533.66354157339</v>
       </c>
     </row>
     <row r="3">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>1119.374131634537</v>
+        <v>988.9561452846611</v>
       </c>
     </row>
     <row r="4">
@@ -3960,31 +3960,31 @@
         <v>80502.49816</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>92464.74916857143</v>
+        <v>89119.68488285714</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>107311.4563147326</v>
+        <v>100929.6163912633</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>124240.2267948082</v>
+        <v>115687.6362130844</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>142859.3821936546</v>
+        <v>133317.8163964851</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>163112.8642584402</v>
+        <v>153905.7844076717</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>185226.9656137432</v>
+        <v>177697.5435292622</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>209675.5815216762</v>
+        <v>205104.3044690556</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>237347.4789805146</v>
+        <v>236713.5502808403</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>269394.5989417836</v>
+        <v>273306.7730339688</v>
       </c>
     </row>
     <row r="3">
@@ -3997,31 +3997,31 @@
         <v>55039.06173834017</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>62994.34796611432</v>
+        <v>60538.36593376451</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>72898.80794517475</v>
+        <v>68213.19270832837</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>84128.90501953494</v>
+        <v>77849.50139537634</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>96355.62019931775</v>
+        <v>89350.10037764777</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>109487.8773112017</v>
+        <v>102727.9406545377</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>123631.6969740675</v>
+        <v>118103.5146212089</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>139062.5929800047</v>
+        <v>135706.3123984697</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>156345.8628748016</v>
+        <v>155880.4256325818</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>176222.1723307616</v>
+        <v>179094.5324581484</v>
       </c>
     </row>
     <row r="4">
@@ -4034,31 +4034,31 @@
         <v>25463.43642165983</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>29470.40120245711</v>
+        <v>28581.31894909263</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>34412.64836955789</v>
+        <v>32716.4236829349</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>40111.32177527326</v>
+        <v>37838.13481770811</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>46503.76199433685</v>
+        <v>43967.71601883737</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>53624.98694723855</v>
+        <v>51177.84375313399</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>61595.26863967572</v>
+        <v>59594.0289080533</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>70612.98854167145</v>
+        <v>69397.9920705859</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>81001.61610571301</v>
+        <v>80833.12464825856</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>93172.42661102201</v>
+        <v>94212.24057582038</v>
       </c>
     </row>
     <row r="5">
@@ -4071,31 +4071,31 @@
         <v>5434.795527759074</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>6242.37777389139</v>
+        <v>6016.549497308791</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>7244.692229270591</v>
+        <v>6813.848517985873</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>8387.568639300927</v>
+        <v>7810.175612914047</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>9644.564444464417</v>
+        <v>9000.404818272322</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>11011.89510206057</v>
+        <v>10390.31692075711</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>12504.83782922092</v>
+        <v>11996.51982162298</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>14155.38571820997</v>
+        <v>13846.77472290456</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>16023.54022262048</v>
+        <v>15980.7431300997</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>18187.06990460499</v>
+        <v>18451.1842705687</v>
       </c>
     </row>
     <row r="6">
@@ -4145,31 +4145,31 @@
         <v>18885.95049390076</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>22071.22128104572</v>
+        <v>21407.96730426384</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>25991.51912246714</v>
+        <v>24726.13814712886</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>30521.05782519213</v>
+        <v>28825.26389401385</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>35622.29393310785</v>
+        <v>33730.40758380046</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>41332.43048592988</v>
+        <v>39506.86547312878</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>47754.53388085766</v>
+        <v>46261.61215683318</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>55052.66742863743</v>
+        <v>54146.28195285729</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>63487.49571407202</v>
+        <v>63361.80134913835</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>73389.14517235501</v>
+        <v>74164.84477118967</v>
       </c>
     </row>
     <row r="8">
@@ -4179,34 +4179,34 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>24854.89925771284</v>
+        <v>26857.8504845959</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>32743.19108644899</v>
+        <v>32623.9332271676</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>36210.03209729883</v>
+        <v>36356.02591193622</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>37358.90075724797</v>
+        <v>38926.70517958818</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>37562.72356223088</v>
+        <v>40966.15127672323</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>37703.15388024685</v>
+        <v>42935.81689718476</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>38340.26262790675</v>
+        <v>45183.34377728002</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>39832.36305608287</v>
+        <v>47983.8439038974</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>42914.74562117796</v>
+        <v>51571.39429315487</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>47810.33193218939</v>
+        <v>56163.65797474995</v>
       </c>
     </row>
     <row r="9">
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1119.374131634537</v>
+        <v>988.9561452846611</v>
       </c>
     </row>
     <row r="14">
@@ -4466,31 +4466,31 @@
         <v>49337.22416</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>54800.46768857143</v>
+        <v>51455.40340285714</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>61789.85626913265</v>
+        <v>55408.01634566326</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>69218.4627711762</v>
+        <v>60665.87218945244</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>76350.33572322357</v>
+        <v>66808.7699260541</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>82712.8343305944</v>
+        <v>73505.7544798258</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>88028.13722106727</v>
+        <v>80498.71513658627</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>92160.0606257667</v>
+        <v>87588.78357314615</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>95259.00317929126</v>
+        <v>94625.07447961702</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>97583.21009443469</v>
+        <v>101495.3841866199</v>
       </c>
     </row>
     <row r="3">
@@ -4604,31 +4604,31 @@
         <v>25463.43642165983</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>29470.40120245711</v>
+        <v>28581.31894909263</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>34412.64836955789</v>
+        <v>32716.4236829349</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>40111.32177527326</v>
+        <v>37838.13481770811</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>46503.76199433685</v>
+        <v>43967.71601883737</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>53624.98694723855</v>
+        <v>51177.84375313399</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>61595.26863967572</v>
+        <v>59594.0289080533</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>70612.98854167145</v>
+        <v>69397.9920705859</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>81001.61610571301</v>
+        <v>80833.12464825856</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>93172.42661102201</v>
+        <v>94212.24057582038</v>
       </c>
     </row>
     <row r="6">
@@ -4650,31 +4650,31 @@
         <v>23122.05950777309</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>30169.34635209502</v>
+        <v>29965.78196025593</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>39539.12828247499</v>
+        <v>38903.73735746867</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>50661.12043045783</v>
+        <v>49784.49386296726</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>63300.70955793542</v>
+        <v>62605.28389967848</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>77468.13637203586</v>
+        <v>77488.82940662616</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>93358.19935873547</v>
+        <v>94669.72995668893</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>111312.6308808015</v>
+        <v>114488.6168876659</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>131828.1223648613</v>
+        <v>137392.8702729778</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>155602.1894433076</v>
+        <v>163943.1670490099</v>
       </c>
     </row>
     <row r="7">
@@ -4696,31 +4696,31 @@
         <v>12667.78110292276</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>16528.74716796406</v>
+        <v>16417.22123943246</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>21662.12840661506</v>
+        <v>21314.01957357371</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>27755.48535484487</v>
+        <v>27275.21181077568</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>34680.28148920053</v>
+        <v>34299.28169075293</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>42442.12734088036</v>
+        <v>42453.46434277922</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>51147.74630010395</v>
+        <v>51866.28880359827</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>60984.36177427862</v>
+        <v>62724.37526690798</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>72224.09391196206</v>
+        <v>75272.8278869468</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>85249.08753654447</v>
+        <v>89818.82227223687</v>
       </c>
     </row>
     <row r="8">
@@ -4742,31 +4742,31 @@
         <v>6.147457230769553</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>8.021117942258936</v>
+        <v>7.966996319048092</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>10.5122599471173</v>
+        <v>10.34332869188105</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>13.46926172404354</v>
+        <v>13.23619319789461</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>16.82974669942157</v>
+        <v>16.64485402193854</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>20.5964375679604</v>
+        <v>20.60193922083332</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>24.82112536327254</v>
+        <v>25.16982173502326</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>29.59466639873162</v>
+        <v>30.43906514859895</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>35.04911592231653</v>
+        <v>36.52861431015089</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>41.36992227250617</v>
+        <v>43.58753628204644</v>
       </c>
     </row>
   </sheetData>

--- a/engine/tmgh_study/TMGH_Valuation_Model_01092026.xlsx
+++ b/engine/tmgh_study/TMGH_Valuation_Model_01092026.xlsx
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -577,6 +577,16 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -640,6 +650,56 @@
           <t>2035</t>
         </is>
       </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -648,34 +708,64 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>107316.3640287191</v>
+        <v>94001.70396492815</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>148389.7381835084</v>
+        <v>116038.9016509047</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>198092.5385168163</v>
+        <v>142860.2477902836</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>256281.5944982783</v>
+        <v>175619.2321762661</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>323422.1792900087</v>
+        <v>215692.9107378501</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>400492.965549311</v>
+        <v>264734.75624807</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>488933.4032206548</v>
+        <v>324737.0687092294</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>590625.1829186812</v>
+        <v>398105.2867650592</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>707902.2030731476</v>
+        <v>487746.9350249625</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>843585.6267175643</v>
+        <v>597178.4394746155</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>730653.6599738663</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>893318.7456604273</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>1091398.841622919</v>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>1332423.295328178</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>1625497.368013205</v>
+      </c>
+      <c r="R2" s="8" t="n">
+        <v>1981630.097126175</v>
+      </c>
+      <c r="S2" s="8" t="n">
+        <v>2414129.938637102</v>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v>2939082.212542546</v>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v>3575925.265721703</v>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v>4348145.755671801</v>
       </c>
     </row>
     <row r="3">
@@ -691,31 +781,61 @@
         <v>147460.4685</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>148374.4597659598</v>
+        <v>154064.053575</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>151962.0039801408</v>
+        <v>167710.48282125</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>158513.0362257171</v>
+        <v>188377.7932839375</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>167936.4917334951</v>
+        <v>216397.2623645531</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>179921.0811647089</v>
+        <v>252434.6476553348</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>194043.8298639381</v>
+        <v>297490.0267998051</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>209841.4955863682</v>
+        <v>352914.3693698185</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>226855.8650375194</v>
+        <v>420441.9961513216</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>244660.8971104994</v>
+        <v>502238.9600622404</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>600968.1755851794</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>719872.8783350834</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>862880.7547267511</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>1034731.88121559</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>1241134.489116324</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>1488953.560682801</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>1786438.40312677</v>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v>2143496.681482681</v>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v>2572023.966077135</v>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v>3086299.720516</v>
       </c>
     </row>
     <row r="4">
@@ -757,6 +877,36 @@
       <c r="L4" s="8" t="n">
         <v>143825.4577268492</v>
       </c>
+      <c r="M4" s="8" t="n">
+        <v>157048.0965738506</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>173179.4800746866</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>192815.2821969625</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>216673.9056420425</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>245621.8118934672</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>280704.0898978051</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>323181.3490805101</v>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v>374574.2478946273</v>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v>436717.2415325486</v>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v>511823.4615922736</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -797,6 +947,36 @@
       <c r="L5" s="8" t="n">
         <v>25228</v>
       </c>
+      <c r="M5" s="8" t="n">
+        <v>25228</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>25228</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>25228</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>25228</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>25228</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>25228</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>25228</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>25228</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>25228</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>25228</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -808,34 +988,64 @@
         <v>477897.9</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>509761.9114887191</v>
+        <v>496447.2514249281</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>553385.5161011482</v>
+        <v>526724.2733775846</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>608864.0517286409</v>
+        <v>569380.2398432174</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>676454.8321210443</v>
+        <v>625657.2268572524</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>756665.3509608455</v>
+        <v>697396.8530397448</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>850323.6908471152</v>
+        <v>787079.0480365001</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>958640.0826532637</v>
+        <v>897889.9450777052</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1083266.592590091</v>
+        <v>1033819.57021992</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1226360.595949168</v>
+        <v>1199791.459014785</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>1390656.881554913</v>
+        <v>1401827.757263705</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>1647254.832132896</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>1944956.004070197</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>2305679.778546633</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>2742413.98218581</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>3270838.569022996</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>3909872.64770678</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>4682334.590844383</v>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v>5615738.041919854</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>6743251.373331387</v>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v>8104853.837780075</v>
       </c>
     </row>
     <row r="7">
@@ -848,34 +1058,64 @@
         <v>133993.1</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>146535.3863118228</v>
+        <v>133220.7262480319</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>165118.3753358257</v>
+        <v>139186.6261836622</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>188087.3794779219</v>
+        <v>151515.2674349126</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>214076.2295505907</v>
+        <v>170186.8079327836</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>241971.2489979393</v>
+        <v>195500.5347775066</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>270876.7987804168</v>
+        <v>228057.9156766326</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>300083.3472709557</v>
+        <v>268762.4542696777</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>329038.5529001899</v>
+        <v>318834.6617169022</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>357321.5343523726</v>
+        <v>379841.3815052493</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>384620.2995907791</v>
+        <v>453739.4983900242</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>542934.7785058228</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>650357.2695353326</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>779555.3749386581</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>934811.438548584</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>1121282.467724946</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>1345170.51736992</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>1613928.287918892</v>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v>1936506.695808911</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>2323652.597700375</v>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v>2788266.539287711</v>
       </c>
     </row>
     <row r="8">
@@ -914,6 +1154,36 @@
       <c r="L8" s="8" t="n">
         <v>16493</v>
       </c>
+      <c r="M8" s="8" t="n">
+        <v>16493</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>16493</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>16493</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>16493</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>16493</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>16493</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>16493</v>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>16493</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>16493</v>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v>16493</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -925,34 +1195,64 @@
         <v>310574.2</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>323116.4863118228</v>
+        <v>309801.8262480319</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>341699.4753358257</v>
+        <v>315767.7261836622</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>364668.4794779219</v>
+        <v>328096.3674349126</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>390657.3295505907</v>
+        <v>346767.9079327836</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>418552.3489979394</v>
+        <v>372081.6347775066</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>447457.8987804168</v>
+        <v>404639.0156766326</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>476664.4472709558</v>
+        <v>445343.5542696777</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>505619.6529001899</v>
+        <v>495415.7617169021</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>533902.6343523726</v>
+        <v>556422.4815052493</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>561201.3995907791</v>
+        <v>630320.5983900242</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>719515.8785058227</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>826938.3695353325</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>956136.4749386581</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>1111392.538548584</v>
+      </c>
+      <c r="Q9" s="8" t="n">
+        <v>1297863.567724946</v>
+      </c>
+      <c r="R9" s="8" t="n">
+        <v>1521751.61736992</v>
+      </c>
+      <c r="S9" s="8" t="n">
+        <v>1790509.387918892</v>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v>2113087.795808911</v>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v>2500233.697700375</v>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v>2964847.639287711</v>
       </c>
     </row>
     <row r="10">
@@ -968,31 +1268,61 @@
         <v>100538.3467720459</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>112030.4016396486</v>
+        <v>111695.6103435446</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>126950.2153411502</v>
+        <v>125613.9297283285</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>146042.8636086932</v>
+        <v>142872.4453250538</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>170052.3607922203</v>
+        <v>164178.9895105747</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>199769.7858321657</v>
+        <v>190395.6572116271</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>236076.1879946845</v>
+        <v>222570.0306813615</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>279983.2506815201</v>
+        <v>261973.1416574971</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>332674.2302023828</v>
+        <v>310145.4989683788</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>395547.4057929487</v>
+        <v>368952.7996783586</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>440653.2876727466</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>527979.1376865178</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>634234.7400238817</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>763415.3593191212</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>920350.3608941813</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>1110876.066100348</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>1342044.344211867</v>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>1622374.309983057</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>1962156.01751277</v>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v>2373816.876405435</v>
       </c>
     </row>
     <row r="11">
@@ -1008,31 +1338,61 @@
         <v>86107.07840485034</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>99655.63912567381</v>
+        <v>99260.93685037787</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>117245.3569095688</v>
+        <v>115669.9426799763</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>139754.6389617604</v>
+        <v>136016.8735994151</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>168060.6411706859</v>
+        <v>161136.2287516634</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>203096.0062345329</v>
+        <v>192044.3751482404</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>245899.4473876235</v>
+        <v>229976.3601266659</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>297663.6890083815</v>
+        <v>276430.6668455202</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>359783.7313944125</v>
+        <v>333223.4785411567</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>433908.0761711855</v>
+        <v>402554.3591953223</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>487085.665954327</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>590038.4968483469</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>715308.5635840928</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>867606.084318105</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>1052624.640403869</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>1277244.964236514</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>1549780.858713624</v>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>1880275.936127887</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>2280861.658118242</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>2766189.322086928</v>
       </c>
     </row>
     <row r="12">
@@ -1048,31 +1408,61 @@
         <v>186645.4251768963</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>211686.0407653225</v>
+        <v>210956.5471939225</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>244195.572250719</v>
+        <v>241283.8724083048</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>285797.5025704536</v>
+        <v>278889.3189244689</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>338113.0019629062</v>
+        <v>325315.2182622381</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>402865.7920666986</v>
+        <v>382440.0323598674</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>481975.635382308</v>
+        <v>452546.3908080274</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>577646.9396899015</v>
+        <v>538403.8085030173</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>692457.9615967954</v>
+        <v>643368.9775095354</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>829455.4819641341</v>
+        <v>771507.1588736809</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>927738.9536270736</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>1118017.634534865</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>1349543.303607974</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>1631021.443637226</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>1972975.00129805</v>
+      </c>
+      <c r="R12" s="8" t="n">
+        <v>2388121.030336861</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>2891825.202925491</v>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v>3502650.246110944</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>4243017.675631013</v>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v>5140006.198492363</v>
       </c>
     </row>
     <row r="13">
@@ -1082,34 +1472,64 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0</v>
+        <v>-5.820766091346741e-11</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>5.820766091346741e-11</v>
+        <v>-2.91038304567337e-11</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="9" t="n">
+        <v>-5.820766091346741e-11</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>1.164153218269348e-10</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>5.820766091346741e-11</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>5.820766091346741e-11</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>1.164153218269348e-10</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>3.492459654808044e-10</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>1.164153218269348e-10</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>1.164153218269348e-10</v>
+      </c>
+      <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>-1.164153218269348e-10</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>-1.746229827404022e-10</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>-1.164153218269348e-10</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>-1.164153218269348e-10</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <v>-1.164153218269348e-10</v>
-      </c>
-      <c r="L13" s="9" t="n">
+      <c r="O13" s="9" t="n">
+        <v>2.328306436538696e-10</v>
+      </c>
+      <c r="P13" s="9" t="n">
         <v>-4.656612873077393e-10</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>-4.656612873077393e-10</v>
+      </c>
+      <c r="R13" s="9" t="n">
+        <v>-9.313225746154785e-10</v>
+      </c>
+      <c r="S13" s="9" t="n">
+        <v>-9.313225746154785e-10</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>-4.656612873077393e-10</v>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>-9.313225746154785e-10</v>
+      </c>
+      <c r="V13" s="9" t="n">
+        <v>1.862645149230957e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1123,7 +1543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1137,6 +1557,16 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1195,6 +1625,56 @@
           <t>2035</t>
         </is>
       </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1203,34 +1683,64 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>37661.9677195959</v>
+        <v>24347.30765580498</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>48791.58186581906</v>
+        <v>29611.92341296168</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>59461.63430320401</v>
+        <v>36150.9682592531</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>70425.00700083998</v>
+        <v>44208.87854643864</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>82313.75145601362</v>
+        <v>54088.43679815016</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>95690.45111713794</v>
+        <v>66161.1857942442</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>111089.4266775959</v>
+        <v>80880.43202764675</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>129051.092189294</v>
+        <v>98797.26552822588</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>150152.0624430299</v>
+        <v>120580.1381727606</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>175033.1117484983</v>
+        <v>147038.6747477692</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>179152.545407998</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>218106.4106378993</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>265332.1671331053</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>322559.9830918054</v>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>391879.923622039</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>475816.3425198153</v>
+      </c>
+      <c r="R2" s="8" t="n">
+        <v>577417.668963057</v>
+      </c>
+      <c r="S2" s="8" t="n">
+        <v>700364.7628104654</v>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v>849101.6695902626</v>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v>1028993.399290783</v>
       </c>
     </row>
     <row r="3">
@@ -1269,6 +1779,36 @@
       <c r="K3" s="8" t="n">
         <v>-12404.04142241051</v>
       </c>
+      <c r="L3" s="8" t="n">
+        <v>-14948.5443397236</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>-18015.96065972214</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>-21713.95588317221</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>-26172.40683144354</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>-31547.99311912926</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>-38029.73974705946</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>-45845.70826147865</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>-55271.07500308329</v>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v>-66637.88461265681</v>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v>-80346.82695811556</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1280,31 +1820,61 @@
         <v>-3800.334330876827</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>-4925.166371829739</v>
+        <v>-4781.684387785156</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>-6394.205872072112</v>
+        <v>-5964.994022050229</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-8182.563543232703</v>
+        <v>-7396.506684310861</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>-10289.78450722588</v>
+        <v>-9131.376079508931</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>-12736.03930283377</v>
+        <v>-11235.71472902245</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-15559.88664107948</v>
+        <v>-13789.01720131475</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>-18817.31258007239</v>
+        <v>-16887.04756120098</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>-22581.84836608404</v>
+        <v>-20645.29599037784</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>-26945.64668167106</v>
+        <v>-25203.12887570566</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>-30728.78056902342</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>-37425.36429161622</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>-45538.11528744164</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>-55363.12255510267</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>-67257.85781788286</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>-81653.87365978552</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>-99072.11919065124</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>-120141.4139019383</v>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v>-145620.7317984488</v>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v>-176426.0823825704</v>
       </c>
     </row>
     <row r="5">
@@ -1314,34 +1884,64 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>12542.28631182281</v>
+        <v>-772.3737519681163</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>18582.98902400291</v>
+        <v>5965.899935630296</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>22969.00414209618</v>
+        <v>12328.64125125037</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>25988.85007266884</v>
+        <v>18671.540497871</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>27895.0194473486</v>
+        <v>25313.72684472305</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>28905.54978247745</v>
+        <v>32557.380899126</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>29206.54849053897</v>
+        <v>40704.53859304514</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>28955.20562923411</v>
+        <v>50072.20744722441</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>28282.98145218274</v>
+        <v>61006.71978834717</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>27298.76523840651</v>
+        <v>73898.11688477488</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>89195.28011579858</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>107422.4910295098</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>129198.1054033255</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>155256.0636099259</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>186471.0291763623</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>223888.0496449734</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>268757.7705489723</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>322578.4078900195</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>387145.9018914632</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>464613.9415873359</v>
       </c>
     </row>
     <row r="6">
@@ -1354,31 +1954,61 @@
         <v>854.9315000000061</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>-913.991265959783</v>
+        <v>-6603.585074999995</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>-3587.544214180998</v>
+        <v>-13646.42924625</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-6551.032245576323</v>
+        <v>-20667.31046268749</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-9423.455507778075</v>
+        <v>-28019.46908061561</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-11984.58943121376</v>
+        <v>-36037.38529078171</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-14122.74869922917</v>
+        <v>-45055.37914447027</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>-15797.66572243007</v>
+        <v>-55424.34257001347</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>-17014.3694511512</v>
+        <v>-67527.62678150306</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>-17805.03207298006</v>
+        <v>-81796.96391091886</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>-98729.21552293893</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>-118904.702749904</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>-143007.8763916678</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>-171851.1264888385</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>-206402.6079007342</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>-247819.071566477</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>-297484.8424439693</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>-357058.2783559109</v>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v>-428527.2845944538</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>-514275.7544388652</v>
       </c>
     </row>
     <row r="7">
@@ -1388,34 +2018,64 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>26857.8504845959</v>
+        <v>13543.19042080498</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>32623.9332271676</v>
+        <v>15508.04708419782</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>36356.02591193622</v>
+        <v>18059.73953053887</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>38926.70517958818</v>
+        <v>21271.58178779941</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>40966.15127672323</v>
+        <v>25243.50277877168</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>42935.81689718476</v>
+        <v>30104.58819987562</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>45183.34377728002</v>
+        <v>36016.87156902326</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>47983.8439038974</v>
+        <v>43180.44909210024</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>51571.39429315487</v>
+        <v>51840.05392669699</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>56163.65797474995</v>
+        <v>62293.28752148946</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>74900.77207470899</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>90098.56180722793</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>108413.2347975669</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>130480.1849338095</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>157065.7488520423</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>189093.9398557091</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>227678.7247720213</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>274162.9764436315</v>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v>330165.4711585112</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>397637.5852708032</v>
       </c>
     </row>
     <row r="8">
@@ -1425,34 +2085,64 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>107316.3640287191</v>
+        <v>94001.70396492815</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>148389.7381835084</v>
+        <v>116038.9016509047</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>198092.5385168163</v>
+        <v>142860.2477902836</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>256281.5944982783</v>
+        <v>175619.2321762661</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>323422.1792900087</v>
+        <v>215692.9107378501</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>400492.965549311</v>
+        <v>264734.75624807</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>488933.4032206548</v>
+        <v>324737.0687092294</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>590625.1829186812</v>
+        <v>398105.2867650592</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>707902.2030731476</v>
+        <v>487746.9350249625</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>843585.6267175643</v>
+        <v>597178.4394746155</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>730653.6599738663</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>893318.7456604273</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>1091398.841622919</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>1332423.295328178</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>1625497.368013205</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>1981630.097126175</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>2414129.938637102</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>2939082.212542546</v>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>3575925.265721703</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>4348145.755671801</v>
       </c>
     </row>
   </sheetData>
@@ -1466,7 +2156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1480,6 +2170,16 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1538,6 +2238,56 @@
           <t>2035</t>
         </is>
       </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1549,31 +2299,61 @@
         <v>80502.49816</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>89119.68488285714</v>
+        <v>96868.950472</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>100929.6163912633</v>
+        <v>116567.202836</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>115687.6362130844</v>
+        <v>140276.487372112</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>133317.8163964851</v>
+        <v>168814.714488607</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>153905.7844076717</v>
+        <v>203166.831549657</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>177697.5435292622</v>
+        <v>244518.9903388493</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>205104.3044690556</v>
+        <v>294299.7152313175</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>236713.5502808403</v>
+        <v>354229.509003713</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>273306.7730339688</v>
+        <v>426380.6286903365</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>513249.1202491786</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>617841.6306003595</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>743780.0340080727</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>895427.5351006094</v>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>1078040.665155656</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>1297952.498289396</v>
+      </c>
+      <c r="R2" s="8" t="n">
+        <v>1562793.512072458</v>
+      </c>
+      <c r="S2" s="8" t="n">
+        <v>1881757.841719673</v>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v>2265924.275287529</v>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v>2728643.265918219</v>
       </c>
     </row>
     <row r="3">
@@ -1586,31 +2366,61 @@
         <v>0.316306164450336</v>
       </c>
       <c r="C3" s="10" t="n">
-        <v>0.3207071365508213</v>
+        <v>0.3163138506187497</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>0.3241508771430039</v>
+        <v>0.3163216217448344</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.3270715528149806</v>
+        <v>0.3163294781657683</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.3297962508482591</v>
+        <v>0.3163374202026129</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>0.3325270973413976</v>
+        <v>0.31634544815982</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>0.3353677700009381</v>
+        <v>0.3163535623247366</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>0.3383546349757671</v>
+        <v>0.3163617629671086</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.3414807667425755</v>
+        <v>0.3163700503385846</v>
       </c>
       <c r="K3" s="10" t="n">
-        <v>0.3447124252720621</v>
+        <v>0.3163784246722187</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>0.3163868861819739</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>0.3163954350622263</v>
+      </c>
+      <c r="N3" s="10" t="n">
+        <v>0.316404071487271</v>
+      </c>
+      <c r="O3" s="10" t="n">
+        <v>0.3164127956108282</v>
+      </c>
+      <c r="P3" s="10" t="n">
+        <v>0.316421607565553</v>
+      </c>
+      <c r="Q3" s="10" t="n">
+        <v>0.3164305074625486</v>
+      </c>
+      <c r="R3" s="10" t="n">
+        <v>0.3164394953908803</v>
+      </c>
+      <c r="S3" s="10" t="n">
+        <v>0.3164485714170964</v>
+      </c>
+      <c r="T3" s="10" t="n">
+        <v>0.3164577355847517</v>
+      </c>
+      <c r="U3" s="10" t="n">
+        <v>0.316466987913937</v>
       </c>
     </row>
     <row r="4">
@@ -1623,31 +2433,61 @@
         <v>0.2346008002927391</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.2402159223565862</v>
+        <v>0.2368610285719238</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.2449839703271598</v>
+        <v>0.2387183788198176</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.2491646025243419</v>
+        <v>0.2402448369002489</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.2530075011391331</v>
+        <v>0.2414995379892343</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>0.2566951308891773</v>
+        <v>0.2425310590634472</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>0.2603390639962059</v>
+        <v>0.2433793026878711</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>0.2639938839558895</v>
+        <v>0.2440770449202446</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.2676728952523631</v>
+        <v>0.2446512071836265</v>
       </c>
       <c r="K4" s="10" t="n">
-        <v>0.2713611666036973</v>
+        <v>0.2451239012997197</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>0.2455132881140143</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>0.2458342829418592</v>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>0.2460991351447717</v>
+      </c>
+      <c r="O4" s="10" t="n">
+        <v>0.2463179042804989</v>
+      </c>
+      <c r="P4" s="10" t="n">
+        <v>0.2464988512710131</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>0.2466487597455195</v>
+      </c>
+      <c r="R4" s="10" t="n">
+        <v>0.2467732000139287</v>
+      </c>
+      <c r="S4" s="10" t="n">
+        <v>0.246876745905884</v>
+      </c>
+      <c r="T4" s="10" t="n">
+        <v>0.2469631528856157</v>
+      </c>
+      <c r="U4" s="10" t="n">
+        <v>0.2470355043532487</v>
       </c>
     </row>
     <row r="5">
@@ -1660,31 +2500,61 @@
         <v>23122.05950777309</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>29965.78196025593</v>
+        <v>29092.80640481138</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>38903.73735746867</v>
+        <v>36292.31923643257</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>49784.49386296726</v>
+        <v>45001.95320047493</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>62605.28389967848</v>
+        <v>55557.27541727814</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>77488.82940662616</v>
+        <v>68360.5288266518</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>94669.72995668893</v>
+        <v>83895.37564947472</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>114488.6168876659</v>
+        <v>102744.4652561909</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>137392.8702729778</v>
+        <v>125610.464996896</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>163943.1670490099</v>
+        <v>153341.3102398511</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>186960.5753224161</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>227704.0451994073</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>277063.7843605513</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>336841.2625843545</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>409211.4154787064</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>496799.9026985973</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>602776.2917792804</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>730966.4570873907</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>885988.1613185176</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>1073414.605243922</v>
       </c>
     </row>
     <row r="6">
@@ -1697,31 +2567,61 @@
         <v>12667.78110292276</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>16417.22123943246</v>
+        <v>15938.94795928385</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>21314.01957357371</v>
+        <v>19883.3134068341</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>27275.21181077568</v>
+        <v>24655.0222810362</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>34299.28169075293</v>
+        <v>30437.92026502977</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>42453.46434277922</v>
+        <v>37452.38243007485</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>51866.28880359827</v>
+        <v>45963.39067104919</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>62724.37526690798</v>
+        <v>56290.15853733661</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>75272.8278869468</v>
+        <v>68817.65330125947</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>89818.82227223687</v>
+        <v>84010.42958568553</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>102429.2685634114</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>124751.2143053874</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>151793.7176248055</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>184543.7418503422</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>224192.8593929429</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>272179.5788659517</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>330240.3973021708</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>400471.3796731276</v>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v>485402.4393281628</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>588086.9412752348</v>
       </c>
     </row>
     <row r="7">
@@ -1734,31 +2634,61 @@
         <v>6.147457230769553</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7.966996319048092</v>
+        <v>7.73489848672487</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>10.34332869188105</v>
+        <v>9.64903149031346</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>13.23619319789461</v>
+        <v>11.96466009042189</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>16.64485402193854</v>
+        <v>14.77100144868089</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>20.60193922083332</v>
+        <v>18.17499981320242</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>25.16982173502326</v>
+        <v>22.30524635969865</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>30.43906514859895</v>
+        <v>27.31664995708479</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>36.52861431015089</v>
+        <v>33.39602862997145</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>43.58753628204644</v>
+        <v>40.76882278123843</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>49.70716991054557</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>60.53962791099961</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>73.66289166322137</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>89.55591756865817</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>108.7969553124076</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>132.0840884897559</v>
+      </c>
+      <c r="R7" s="9" t="n">
+        <v>160.2600093728363</v>
+      </c>
+      <c r="S7" s="9" t="n">
+        <v>194.3419023967672</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>235.5574911846729</v>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>285.3885214853823</v>
       </c>
     </row>
     <row r="8">
@@ -1768,34 +2698,64 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>183838.2</v>
+        <v>49732.59775999999</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>183838.2</v>
+        <v>75979.88837866664</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>183838.2</v>
+        <v>104759.8419432889</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>183838.2</v>
+        <v>137031.7902393541</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>183838.2</v>
+        <v>173871.464876731</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>183838.2</v>
+        <v>216506.8550099991</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>183838.2</v>
+        <v>266359.140310267</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>183838.2</v>
+        <v>325090.0636208772</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>183838.2</v>
+        <v>394657.3223855167</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>183838.2</v>
+        <v>477379.8252296733</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>576014.988914819</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>693850.6522304586</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>834814.670620447</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>1003605.844697784</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>1205850.546931713</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>1448290.267396699</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>1739006.330108242</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>2087689.27049006</v>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>2505961.853221547</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>3007766.497727085</v>
       </c>
     </row>
     <row r="9">
@@ -1805,34 +2765,64 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>625500.97584</v>
+        <v>491395.3736</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>757883.7724371428</v>
+        <v>508170.5929866667</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>886313.9560914795</v>
+        <v>541884.8321395555</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1009486.283902027</v>
+        <v>593661.8990304295</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>1126515.713975973</v>
+        <v>665227.6958889846</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>1236848.159496147</v>
+        <v>758967.7492771724</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1340187.644359561</v>
+        <v>878006.727641266</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>1436437.060786415</v>
+        <v>1026312.596926735</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>1525650.186306798</v>
+        <v>1208828.886109762</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>1607993.002120178</v>
+        <v>1431639.471496448</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>1702171.372599682</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>2029442.319456238</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>2424361.343628003</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>2900092.412587367</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>3472493.228632978</v>
+      </c>
+      <c r="Q9" s="8" t="n">
+        <v>4160643.818966353</v>
+      </c>
+      <c r="R9" s="8" t="n">
+        <v>4987482.536598608</v>
+      </c>
+      <c r="S9" s="8" t="n">
+        <v>5980570.672117482</v>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v>7173011.163373607</v>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v>8604552.026742186</v>
       </c>
     </row>
     <row r="10">
@@ -1842,34 +2832,64 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>12.67807393888858</v>
+        <v>9.959931511477237</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>14.72894433464028</v>
+        <v>8.583285771859192</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>15.99613223043764</v>
+        <v>7.627281786013327</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>16.6401017156651</v>
+        <v>6.963390129175921</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>16.86179397140276</v>
+        <v>6.502354256372167</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>16.82654872735997</v>
+        <v>6.182190455814006</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>16.64855944701225</v>
+        <v>5.95985448320417</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>16.3997831935505</v>
+        <v>5.805454502225119</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>16.12310684770383</v>
+        <v>5.698232293211889</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>15.8430160642927</v>
+        <v>5.623772425841589</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>5.572064184612215</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>5.536155683758483</v>
+      </c>
+      <c r="N10" s="9" t="n">
+        <v>5.51121922483228</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>5.493902239466861</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>5.481876555185321</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>5.473525385545361</v>
+      </c>
+      <c r="R10" s="9" t="n">
+        <v>5.467725962184279</v>
+      </c>
+      <c r="S10" s="9" t="n">
+        <v>5.463698584850193</v>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v>5.460901795034857</v>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>5.458959579885319</v>
       </c>
     </row>
   </sheetData>
@@ -2037,13 +3057,13 @@
     </row>
     <row r="2">
       <c r="A2" s="20" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>201.6036914169526</v>
+        <v>156.0838105097744</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>189.998087394918</v>
+        <v>237.8217269820379</v>
       </c>
       <c r="D2" s="10">
         <f>B2/'Summary'!$B$2-1</f>
@@ -2052,13 +3072,13 @@
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>112.6846705623544</v>
+        <v>105.9103422088017</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>102.0012224605793</v>
+        <v>153.406106835808</v>
       </c>
       <c r="D3" s="10">
         <f>B3/'Summary'!$B$2-1</f>
@@ -2067,13 +3087,13 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>84.40119551906773</v>
+        <v>80.87409058419072</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>74.73108003622716</v>
+        <v>112.1456638392772</v>
       </c>
       <c r="D4" s="10">
         <f>B4/'Summary'!$B$2-1</f>
@@ -2082,13 +3102,13 @@
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
-        <v>0.3</v>
+        <v>0.3157</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>69.20894631831915</v>
+        <v>57.75526827071646</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>60.52657784743045</v>
+        <v>75.17953446617932</v>
       </c>
       <c r="D5" s="10">
         <f>B5/'Summary'!$B$2-1</f>
@@ -2100,10 +3120,10 @@
         <v>0.3237</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>62.9177551183162</v>
+        <v>54.41105716024056</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>54.78614785024519</v>
+        <v>69.98160596090575</v>
       </c>
       <c r="D6" s="10">
         <f>B6/'Summary'!$B$2-1</f>
@@ -2115,10 +3135,10 @@
         <v>0.3579</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>55.87736705533258</v>
+        <v>43.94753340268149</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>48.48386209848692</v>
+        <v>54.09019265766425</v>
       </c>
       <c r="D7" s="10">
         <f>B7/'Summary'!$B$2-1</f>
@@ -2130,10 +3150,10 @@
         <v>0.4</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>49.34699464482212</v>
+        <v>35.99240529135729</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>42.76571683996426</v>
+        <v>42.5113807850869</v>
       </c>
       <c r="D8" s="10">
         <f>B8/'Summary'!$B$2-1</f>
@@ -2157,7 +3177,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>46.41982156593504</v>
+        <v>43.93936943614966</v>
       </c>
     </row>
     <row r="12">
@@ -2165,7 +3185,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>50.65079038861755</v>
+        <v>43.93936943614966</v>
       </c>
     </row>
     <row r="13">
@@ -2173,7 +3193,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>53.64100588478227</v>
+        <v>43.93936943614966</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +3201,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>55.87125667167204</v>
+        <v>43.93936943614966</v>
       </c>
     </row>
     <row r="15">
@@ -2189,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>57.60028647411903</v>
+        <v>43.93936943614966</v>
       </c>
     </row>
     <row r="16">
@@ -2197,7 +3217,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>60.10808915327755</v>
+        <v>43.93936943614966</v>
       </c>
     </row>
   </sheetData>
@@ -2660,17 +3680,17 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>103490.2173712564</v>
+        <v>78902.72859820566</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>115131.3173712563</v>
+        <v>90543.82859820565</v>
       </c>
       <c r="D7" s="9">
         <f>C7/$B$3</f>
         <v/>
       </c>
       <c r="E7" s="9" t="n">
-        <v>50.72370923510034</v>
+        <v>44.18664184956641</v>
       </c>
       <c r="F7" s="10">
         <f>D7/$B$2-1</f>
@@ -2684,17 +3704,17 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>88256.20771011799</v>
+        <v>99795.05149032849</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>99897.307710118</v>
+        <v>111436.1514903285</v>
       </c>
       <c r="D8" s="9">
         <f>C8/$B$3</f>
         <v/>
       </c>
       <c r="E8" s="9" t="n">
-        <v>46.67344820088329</v>
+        <v>49.74127672288594</v>
       </c>
       <c r="F8" s="10">
         <f>D8/$B$2-1</f>
@@ -2708,17 +3728,17 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>117986.9049356308</v>
+        <v>100442.1462520464</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>129628.0049356308</v>
+        <v>112083.2462520464</v>
       </c>
       <c r="D9" s="9">
         <f>C9/$B$3</f>
         <v/>
       </c>
       <c r="E9" s="9" t="n">
-        <v>54.57793869098589</v>
+        <v>49.91331958994005</v>
       </c>
       <c r="F9" s="10">
         <f>D9/$B$2-1</f>
@@ -2732,17 +3752,17 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>101232.7379730227</v>
+        <v>132506.2759098136</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>112873.8379730227</v>
+        <v>144147.3759098136</v>
       </c>
       <c r="D10" s="9">
         <f>C10/$B$3</f>
         <v/>
       </c>
       <c r="E10" s="9" t="n">
-        <v>50.12351394537711</v>
+        <v>58.43819897742189</v>
       </c>
       <c r="F10" s="10">
         <f>D10/$B$2-1</f>
@@ -2778,7 +3798,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.237271115555085</v>
+        <v>0.2652836941995044</v>
       </c>
     </row>
     <row r="16">
@@ -2788,7 +3808,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.2243557037726325</v>
+        <v>0.2907215393505239</v>
       </c>
     </row>
     <row r="17">
@@ -2850,10 +3870,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>48.47845266881705</v>
+        <v>43.93936943614966</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>62.90625088776715</v>
+        <v>69.95225297418403</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
@@ -3153,7 +4173,7 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -3228,7 +4248,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>94533.66354157339</v>
+        <v>72255.83250671037</v>
       </c>
     </row>
     <row r="3">
@@ -3238,7 +4258,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>988.9561452846611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3248,7 +4268,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>7967.597684398287</v>
+        <v>6646.896091495293</v>
       </c>
     </row>
     <row r="5">
@@ -3877,7 +4897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3891,6 +4911,16 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3949,6 +4979,56 @@
           <t>2035</t>
         </is>
       </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -3960,31 +5040,61 @@
         <v>80502.49816</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>89119.68488285714</v>
+        <v>96868.950472</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>100929.6163912633</v>
+        <v>116567.202836</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>115687.6362130844</v>
+        <v>140276.487372112</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>133317.8163964851</v>
+        <v>168814.714488607</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>153905.7844076717</v>
+        <v>203166.831549657</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>177697.5435292622</v>
+        <v>244518.9903388493</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>205104.3044690556</v>
+        <v>294299.7152313175</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>236713.5502808403</v>
+        <v>354229.509003713</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>273306.7730339688</v>
+        <v>426380.6286903365</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>513249.1202491786</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>617841.6306003595</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>743780.0340080727</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>895427.5351006094</v>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>1078040.665155656</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>1297952.498289396</v>
+      </c>
+      <c r="R2" s="8" t="n">
+        <v>1562793.512072458</v>
+      </c>
+      <c r="S2" s="8" t="n">
+        <v>1881757.841719673</v>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v>2265924.275287529</v>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v>2728643.265918219</v>
       </c>
     </row>
     <row r="3">
@@ -3997,31 +5107,61 @@
         <v>55039.06173834017</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>60538.36593376451</v>
+        <v>66227.95974280473</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>68213.19270832837</v>
+        <v>79694.47619265741</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>77849.50139537634</v>
+        <v>95902.89932276482</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>89350.10037764777</v>
+        <v>115412.3032150404</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>102727.9406545377</v>
+        <v>138895.9291718701</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>118103.5146212089</v>
+        <v>167164.5366891065</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>135706.3123984697</v>
+        <v>201194.5384800199</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>155880.4256325818</v>
+        <v>242161.9014087962</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>179094.5324581484</v>
+        <v>291482.9970745377</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>350863.8292579035</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>422359.3590870035</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>508445.0029569776</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>612102.8054525126</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>736925.3048660655</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>887240.7305933998</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>1068263.921712108</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>1286278.260954564</v>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v>1548855.010123518</v>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v>1865117.750461433</v>
       </c>
     </row>
     <row r="4">
@@ -4034,31 +5174,61 @@
         <v>25463.43642165983</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>28581.31894909263</v>
+        <v>30640.99072919527</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>32716.4236829349</v>
+        <v>36872.72664334257</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>37838.13481770811</v>
+        <v>44373.58804934718</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>43967.71601883737</v>
+        <v>53402.4112735666</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>51177.84375313399</v>
+        <v>64270.9023777869</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>59594.0289080533</v>
+        <v>77354.45364974285</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>69397.9920705859</v>
+        <v>93105.17675129764</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>80833.12464825856</v>
+        <v>112067.6075949168</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>94212.24057582038</v>
+        <v>134897.6316157989</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>162385.2909912751</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>195482.2715133561</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>235335.0310510951</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>283324.7296480968</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>341115.3602895909</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>410711.7676959964</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>494529.5903603502</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>595479.580765109</v>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v>717069.2651640109</v>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v>863525.5154567866</v>
       </c>
     </row>
     <row r="5">
@@ -4071,31 +5241,61 @@
         <v>5434.795527759074</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>6016.549497308791</v>
+        <v>6539.709336194602</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>6813.848517985873</v>
+        <v>7869.555940951652</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>7810.175612914047</v>
+        <v>9470.190908914105</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>9000.404818272322</v>
+        <v>11396.83210201891</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>10390.31692075711</v>
+        <v>13715.97419623551</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>11996.51982162298</v>
+        <v>16507.69535753426</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>13846.77472290456</v>
+        <v>19868.43654194412</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>15980.7431300997</v>
+        <v>23914.35042807461</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>18451.1842705687</v>
+        <v>28785.33693853437</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>34649.90636455193</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>41711.04012420138</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>50213.2541828633</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>60451.11238069835</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>72779.48783757816</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>87625.93204159674</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>105505.5853464497</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>127039.1520295107</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>152974.5709642134</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>184213.1431621929</v>
       </c>
     </row>
     <row r="6">
@@ -4134,6 +5334,36 @@
       <c r="K6" s="8" t="n">
         <v>1596.211534062009</v>
       </c>
+      <c r="L6" s="8" t="n">
+        <v>1725.905492722191</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>1884.577158886208</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>2078.153760896239</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>2313.78338636355</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>2600.08686770451</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>2947.461742721607</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>3368.449078773661</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>3878.176188966121</v>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v>4494.890974735527</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>5240.606898390583</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4145,31 +5375,61 @@
         <v>18885.95049390076</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>21407.96730426384</v>
+        <v>22944.47924548067</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>24726.13814712886</v>
+        <v>27826.73368457076</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>28825.26389401385</v>
+        <v>33700.70182965287</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>33730.40758380046</v>
+        <v>40768.6755547831</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>39506.86547312878</v>
+        <v>49274.26682230329</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>46261.61215683318</v>
+        <v>59510.86136261145</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>54146.28195285729</v>
+        <v>71831.80481452947</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>63361.80134913835</v>
+        <v>86662.67699782166</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>74164.84477118967</v>
+        <v>104516.0831432025</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>126009.479134001</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>151886.6542302685</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>183043.6231073356</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>220559.8338810349</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>265735.7855843082</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>320138.3739116781</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>385655.5559351268</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>464562.2525466323</v>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v>559599.803225062</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>674071.7653962031</v>
       </c>
     </row>
     <row r="8">
@@ -4179,34 +5439,64 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>26857.8504845959</v>
+        <v>13543.19042080498</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>32623.9332271676</v>
+        <v>15508.04708419782</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>36356.02591193622</v>
+        <v>18059.73953053887</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>38926.70517958818</v>
+        <v>21271.58178779941</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>40966.15127672323</v>
+        <v>25243.50277877168</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>42935.81689718476</v>
+        <v>30104.58819987562</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>45183.34377728002</v>
+        <v>36016.87156902326</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>47983.8439038974</v>
+        <v>43180.44909210024</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>51571.39429315487</v>
+        <v>51840.05392669699</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>56163.65797474995</v>
+        <v>62293.28752148946</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>74900.77207470899</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>90098.56180722793</v>
+      </c>
+      <c r="N8" s="8" t="n">
+        <v>108413.2347975669</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>130480.1849338095</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>157065.7488520423</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>189093.9398557091</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>227678.7247720213</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>274162.9764436315</v>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>330165.4711585112</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>397637.5852708032</v>
       </c>
     </row>
     <row r="9">
@@ -4255,6 +5545,46 @@
         <f>1/(1+'Summary'!$B$14)^10</f>
         <v/>
       </c>
+      <c r="L9" s="19">
+        <f>1/(1+'Summary'!$B$14)^11</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
+        <f>1/(1+'Summary'!$B$14)^12</f>
+        <v/>
+      </c>
+      <c r="N9" s="19">
+        <f>1/(1+'Summary'!$B$14)^13</f>
+        <v/>
+      </c>
+      <c r="O9" s="19">
+        <f>1/(1+'Summary'!$B$14)^14</f>
+        <v/>
+      </c>
+      <c r="P9" s="19">
+        <f>1/(1+'Summary'!$B$14)^15</f>
+        <v/>
+      </c>
+      <c r="Q9" s="19">
+        <f>1/(1+'Summary'!$B$14)^16</f>
+        <v/>
+      </c>
+      <c r="R9" s="19">
+        <f>1/(1+'Summary'!$B$14)^17</f>
+        <v/>
+      </c>
+      <c r="S9" s="19">
+        <f>1/(1+'Summary'!$B$14)^18</f>
+        <v/>
+      </c>
+      <c r="T9" s="19">
+        <f>1/(1+'Summary'!$B$14)^19</f>
+        <v/>
+      </c>
+      <c r="U9" s="19">
+        <f>1/(1+'Summary'!$B$14)^20</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -4302,6 +5632,46 @@
         <f>K8*K9</f>
         <v/>
       </c>
+      <c r="L10" s="8">
+        <f>L8*L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="8">
+        <f>M8*M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="8">
+        <f>N8*N9</f>
+        <v/>
+      </c>
+      <c r="O10" s="8">
+        <f>O8*O9</f>
+        <v/>
+      </c>
+      <c r="P10" s="8">
+        <f>P8*P9</f>
+        <v/>
+      </c>
+      <c r="Q10" s="8">
+        <f>Q8*Q9</f>
+        <v/>
+      </c>
+      <c r="R10" s="8">
+        <f>R8*R9</f>
+        <v/>
+      </c>
+      <c r="S10" s="8">
+        <f>S8*S9</f>
+        <v/>
+      </c>
+      <c r="T10" s="8">
+        <f>T8*T9</f>
+        <v/>
+      </c>
+      <c r="U10" s="8">
+        <f>U8*U9</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -4310,7 +5680,7 @@
         </is>
       </c>
       <c r="B12" s="17">
-        <f>SUM(B10:K10)</f>
+        <f>SUM(B10:U10)</f>
         <v/>
       </c>
     </row>
@@ -4321,7 +5691,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>988.9561452846611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4331,7 +5701,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>7967.597684398287</v>
+        <v>6646.896091495293</v>
       </c>
     </row>
     <row r="15">
@@ -4356,7 +5726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4373,6 +5743,16 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4446,6 +5826,56 @@
           <t>2035</t>
         </is>
       </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -4466,31 +5896,61 @@
         <v>49337.22416</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>51455.40340285714</v>
+        <v>59204.66899199999</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>55408.01634566326</v>
+        <v>71045.60279039999</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>60665.87218945244</v>
+        <v>85254.72334847999</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>66808.7699260541</v>
+        <v>102305.668018176</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>73505.7544798258</v>
+        <v>122766.8016218112</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>80498.71513658627</v>
+        <v>147320.1619461734</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>87588.78357314615</v>
+        <v>176784.1943354081</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>94625.07447961702</v>
+        <v>212141.0332024897</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>101495.3841866199</v>
+        <v>254569.2398429876</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>305483.0878115851</v>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>366579.7053739021</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>439895.6464486825</v>
+      </c>
+      <c r="R2" s="8" t="n">
+        <v>527874.775738419</v>
+      </c>
+      <c r="S2" s="8" t="n">
+        <v>633449.7308861028</v>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v>760139.6770633233</v>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v>912167.612475988</v>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v>1094601.134971186</v>
+      </c>
+      <c r="W2" s="8" t="n">
+        <v>1313521.361965423</v>
+      </c>
+      <c r="X2" s="8" t="n">
+        <v>1576225.634358507</v>
       </c>
     </row>
     <row r="3">
@@ -4538,6 +5998,36 @@
       <c r="N3" s="8" t="n">
         <v>92193.09780860925</v>
       </c>
+      <c r="O3" s="8" t="n">
+        <v>110631.7173703311</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>132758.0608443973</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>159309.6730132768</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>191171.6076159321</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>229405.9291391185</v>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v>275287.1149669422</v>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v>330344.5379603306</v>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v>396413.4455523968</v>
+      </c>
+      <c r="W3" s="8" t="n">
+        <v>475696.1346628761</v>
+      </c>
+      <c r="X3" s="8" t="n">
+        <v>570835.3615954514</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -4584,6 +6074,36 @@
       <c r="N4" s="8" t="n">
         <v>79618.29103873967</v>
       </c>
+      <c r="O4" s="8" t="n">
+        <v>97134.31506726239</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>118503.8643820601</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>144574.7145461133</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>176381.1517462583</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>215185.0051304351</v>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v>262525.7062591308</v>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v>320281.3616361396</v>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v>390743.2611960902</v>
+      </c>
+      <c r="W4" s="8" t="n">
+        <v>476706.7786592301</v>
+      </c>
+      <c r="X4" s="8" t="n">
+        <v>581582.2699642607</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4604,31 +6124,61 @@
         <v>25463.43642165983</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>28581.31894909263</v>
+        <v>30640.99072919527</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>32716.4236829349</v>
+        <v>36872.72664334257</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>37838.13481770811</v>
+        <v>44373.58804934718</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>43967.71601883737</v>
+        <v>53402.4112735666</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>51177.84375313399</v>
+        <v>64270.9023777869</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>59594.0289080533</v>
+        <v>77354.45364974285</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>69397.9920705859</v>
+        <v>93105.17675129764</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>80833.12464825856</v>
+        <v>112067.6075949168</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>94212.24057582038</v>
+        <v>134897.6316157989</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>162385.2909912751</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>195482.2715133561</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>235335.0310510951</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>283324.7296480968</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>341115.3602895909</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>410711.7676959964</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>494529.5903603502</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>595479.580765109</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>717069.2651640109</v>
+      </c>
+      <c r="X5" s="8" t="n">
+        <v>863525.5154567866</v>
       </c>
     </row>
     <row r="6">
@@ -4650,31 +6200,61 @@
         <v>23122.05950777309</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>29965.78196025593</v>
+        <v>29092.80640481138</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>38903.73735746867</v>
+        <v>36292.31923643257</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>49784.49386296726</v>
+        <v>45001.95320047493</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>62605.28389967848</v>
+        <v>55557.27541727814</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>77488.82940662616</v>
+        <v>68360.5288266518</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>94669.72995668893</v>
+        <v>83895.37564947472</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>114488.6168876659</v>
+        <v>102744.4652561909</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>137392.8702729778</v>
+        <v>125610.464996896</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>163943.1670490099</v>
+        <v>153341.3102398511</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>186960.5753224161</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>227704.0451994073</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>277063.7843605513</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>336841.2625843545</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>409211.4154787064</v>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v>496799.9026985973</v>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v>602776.2917792804</v>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v>730966.4570873907</v>
+      </c>
+      <c r="W6" s="8" t="n">
+        <v>885988.1613185176</v>
+      </c>
+      <c r="X6" s="8" t="n">
+        <v>1073414.605243922</v>
       </c>
     </row>
     <row r="7">
@@ -4696,31 +6276,61 @@
         <v>12667.78110292276</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>16417.22123943246</v>
+        <v>15938.94795928385</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>21314.01957357371</v>
+        <v>19883.3134068341</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>27275.21181077568</v>
+        <v>24655.0222810362</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>34299.28169075293</v>
+        <v>30437.92026502977</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>42453.46434277922</v>
+        <v>37452.38243007485</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>51866.28880359827</v>
+        <v>45963.39067104919</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>62724.37526690798</v>
+        <v>56290.15853733661</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>75272.8278869468</v>
+        <v>68817.65330125947</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>89818.82227223687</v>
+        <v>84010.42958568553</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>102429.2685634114</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>124751.2143053874</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>151793.7176248055</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>184543.7418503422</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>224192.8593929429</v>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v>272179.5788659517</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>330240.3973021708</v>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v>400471.3796731276</v>
+      </c>
+      <c r="W7" s="8" t="n">
+        <v>485402.4393281628</v>
+      </c>
+      <c r="X7" s="8" t="n">
+        <v>588086.9412752348</v>
       </c>
     </row>
     <row r="8">
@@ -4742,31 +6352,61 @@
         <v>6.147457230769553</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>7.966996319048092</v>
+        <v>7.73489848672487</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>10.34332869188105</v>
+        <v>9.64903149031346</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>13.23619319789461</v>
+        <v>11.96466009042189</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>16.64485402193854</v>
+        <v>14.77100144868089</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>20.60193922083332</v>
+        <v>18.17499981320242</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>25.16982173502326</v>
+        <v>22.30524635969865</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>30.43906514859895</v>
+        <v>27.31664995708479</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>36.52861431015089</v>
+        <v>33.39602862997145</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>43.58753628204644</v>
+        <v>40.76882278123843</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>49.70716991054557</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>60.53962791099961</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>73.66289166322137</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>89.55591756865817</v>
+      </c>
+      <c r="S8" s="9" t="n">
+        <v>108.7969553124076</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>132.0840884897559</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>160.2600093728363</v>
+      </c>
+      <c r="V8" s="9" t="n">
+        <v>194.3419023967672</v>
+      </c>
+      <c r="W8" s="9" t="n">
+        <v>235.5574911846729</v>
+      </c>
+      <c r="X8" s="9" t="n">
+        <v>285.3885214853823</v>
       </c>
     </row>
   </sheetData>

--- a/engine/tmgh_study/TMGH_Valuation_Model_01092026.xlsx
+++ b/engine/tmgh_study/TMGH_Valuation_Model_01092026.xlsx
@@ -708,64 +708,64 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>94001.70396492815</v>
+        <v>94007.06392117839</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>116038.9016509047</v>
+        <v>115942.9837642265</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>142860.2477902836</v>
+        <v>142349.2808961654</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>175619.2321762661</v>
+        <v>174040.8523455015</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>215692.9107378501</v>
+        <v>211880.0991718504</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>264734.75624807</v>
+        <v>256776.0908634245</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>324737.0687092294</v>
+        <v>309683.3345392122</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>398105.2867650592</v>
+        <v>371601.4510400648</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>487746.9350249625</v>
+        <v>443577.1399989407</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>597178.4394746155</v>
+        <v>526709.8119975199</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>730653.6599738663</v>
+        <v>622162.1578588361</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>893318.7456604273</v>
+        <v>731523.3703117218</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>1091398.841622919</v>
+        <v>856607.5325377719</v>
       </c>
       <c r="P2" s="8" t="n">
-        <v>1332423.295328178</v>
+        <v>999478.812608933</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>1625497.368013205</v>
+        <v>1162480.945937615</v>
       </c>
       <c r="R2" s="8" t="n">
-        <v>1981630.097126175</v>
+        <v>1348271.307092299</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>2414129.938637102</v>
+        <v>1559859.974991126</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>2939082.212542546</v>
+        <v>1800654.295541997</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>3575925.265721703</v>
+        <v>2074509.546888571</v>
       </c>
       <c r="V2" s="8" t="n">
-        <v>4348145.755671801</v>
+        <v>2385786.417662771</v>
       </c>
     </row>
     <row r="3">
@@ -781,61 +781,61 @@
         <v>147460.4685</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>154064.053575</v>
+        <v>153484.470879</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>167710.48282125</v>
+        <v>165207.844739922</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>188377.7932839375</v>
+        <v>181614.7378558756</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>216397.2623645531</v>
+        <v>201768.3118777679</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>252434.6476553348</v>
+        <v>224750.3634124904</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>297490.0267998051</v>
+        <v>249623.0115319655</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>352914.3693698185</v>
+        <v>275410.7986511603</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>420441.9961513216</v>
+        <v>301101.5738707139</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>502238.9600622404</v>
+        <v>325664.0898787904</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>600968.1755851794</v>
+        <v>348079.4932638779</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>719872.8783350834</v>
+        <v>369044.302836885</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>862880.7547267511</v>
+        <v>389087.2973321993</v>
       </c>
       <c r="P3" s="8" t="n">
-        <v>1034731.88121559</v>
+        <v>408611.7060118665</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>1241134.489116324</v>
+        <v>427926.8618421255</v>
       </c>
       <c r="R3" s="8" t="n">
-        <v>1488953.560682801</v>
+        <v>447271.9520081489</v>
       </c>
       <c r="S3" s="8" t="n">
-        <v>1786438.40312677</v>
+        <v>466833.8418577285</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>2143496.681482681</v>
+        <v>486760.454358978</v>
       </c>
       <c r="U3" s="8" t="n">
-        <v>2572023.966077135</v>
+        <v>507170.8166535423</v>
       </c>
       <c r="V3" s="8" t="n">
-        <v>3086299.720516</v>
+        <v>528162.6074098379</v>
       </c>
     </row>
     <row r="4">
@@ -848,64 +848,64 @@
         <v>73322.7</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>96400.17895999999</v>
+        <v>96401.92291199999</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>98036.41815167999</v>
+        <v>98005.10601417215</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>100224.6092316838</v>
+        <v>100067.7869536358</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>103075.3013970489</v>
+        <v>102615.6947613896</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>106721.7799373416</v>
+        <v>105663.3517812658</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>111324.7441330953</v>
+        <v>109211.3392928265</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>117077.9495686708</v>
+        <v>113243.9788584783</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>124215.0140850418</v>
+        <v>117727.6898441762</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>133017.6278385007</v>
+        <v>122610.2643199192</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>143825.4577268492</v>
+        <v>127821.2508016575</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>157048.0965738506</v>
+        <v>133273.5590691119</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>173179.4800746866</v>
+        <v>138978.6703290248</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>192815.2821969625</v>
+        <v>144948.638250117</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>216673.9056420425</v>
+        <v>151196.1187203492</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>245621.8118934672</v>
+        <v>157734.4012117833</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>280704.0898978051</v>
+        <v>164577.4418427168</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>323181.3490805101</v>
+        <v>171739.8982318908</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>374574.2478946273</v>
+        <v>179237.1662450048</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>436717.2415325486</v>
+        <v>187085.4187395119</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>511823.4615922736</v>
+        <v>195301.6464197505</v>
       </c>
     </row>
     <row r="5">
@@ -988,64 +988,64 @@
         <v>477897.9</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>496447.2514249281</v>
+        <v>496454.3553331784</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>526724.2733775846</v>
+        <v>526017.4606573987</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>569380.2398432174</v>
+        <v>566209.8125897233</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>625657.2268572524</v>
+        <v>616856.1849627667</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>697396.8530397448</v>
+        <v>677896.662830884</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>787079.0480365001</v>
+        <v>749322.6935687414</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>897889.9450777052</v>
+        <v>831135.224929656</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1033819.57021992</v>
+        <v>923324.8395354013</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1199791.459014785</v>
+        <v>1025873.878189574</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>1401827.757263705</v>
+        <v>1138780.052677968</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>1647254.832132896</v>
+        <v>1262100.110191826</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>1944956.004070197</v>
+        <v>1398131.243477632</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>2305679.778546633</v>
+        <v>1549228.368120088</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>2742413.98218581</v>
+        <v>1717871.537341149</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>3270838.569022996</v>
+        <v>1906727.108991524</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>3909872.64770678</v>
+        <v>2118705.600943165</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>4682334.590844383</v>
+        <v>2357018.615080745</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>5615738.041919854</v>
+        <v>2625236.816145979</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>6743251.373331387</v>
+        <v>2927350.682281625</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>8104853.837780075</v>
+        <v>3267835.57149236</v>
       </c>
     </row>
     <row r="7">
@@ -1061,61 +1061,61 @@
         <v>133220.7262480319</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>139186.6261836622</v>
+        <v>138663.0117636937</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>151515.2674349126</v>
+        <v>149254.3003694885</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>170186.8079327836</v>
+        <v>164076.8371389359</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>195500.5347775066</v>
+        <v>182284.2509292288</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>228057.9156766326</v>
+        <v>203047.0060409517</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>268762.4542696777</v>
+        <v>225517.7894305231</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>318834.6617169022</v>
+        <v>248815.3400438849</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>379841.3815052493</v>
+        <v>272025.2468578176</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>453739.4983900242</v>
+        <v>294215.8465104618</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>542934.7785058228</v>
+        <v>314466.6727046289</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>650357.2695353326</v>
+        <v>333406.9838631256</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>779555.3749386581</v>
+        <v>351514.4964053842</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>934811.438548584</v>
+        <v>369153.5011523997</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>1121282.467724946</v>
+        <v>386603.4598665959</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>1345170.51736992</v>
+        <v>404080.4622623348</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>1613928.287918892</v>
+        <v>421753.3287536345</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>1936506.695808911</v>
+        <v>439755.6979043846</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>2323652.597700375</v>
+        <v>458195.1028210137</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>2788266.539287711</v>
+        <v>477159.7896841943</v>
       </c>
     </row>
     <row r="8">
@@ -1198,61 +1198,61 @@
         <v>309801.8262480319</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>315767.7261836622</v>
+        <v>315244.1117636937</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>328096.3674349126</v>
+        <v>325835.4003694885</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>346767.9079327836</v>
+        <v>340657.9371389359</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>372081.6347775066</v>
+        <v>358865.3509292288</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>404639.0156766326</v>
+        <v>379628.1060409517</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>445343.5542696777</v>
+        <v>402098.8894305231</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>495415.7617169021</v>
+        <v>425396.4400438849</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>556422.4815052493</v>
+        <v>448606.3468578176</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>630320.5983900242</v>
+        <v>470796.9465104617</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>719515.8785058227</v>
+        <v>491047.7727046289</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>826938.3695353325</v>
+        <v>509988.0838631255</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>956136.4749386581</v>
+        <v>528095.5964053841</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>1111392.538548584</v>
+        <v>545734.6011523997</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>1297863.567724946</v>
+        <v>563184.5598665959</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>1521751.61736992</v>
+        <v>580661.5622623347</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>1790509.387918892</v>
+        <v>598334.4287536346</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>2113087.795808911</v>
+        <v>616336.7979043847</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>2500233.697700375</v>
+        <v>634776.2028210136</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>2964847.639287711</v>
+        <v>653740.8896841943</v>
       </c>
     </row>
     <row r="10">
@@ -1265,64 +1265,64 @@
         <v>91670.89999999999</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>100538.3467720459</v>
+        <v>100541.6070155131</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>111695.6103435446</v>
+        <v>111611.5339393398</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>125613.9297283285</v>
+        <v>125196.5451658646</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>142872.4453250538</v>
+        <v>141637.4143158543</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>164178.9895105747</v>
+        <v>161295.0749189513</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>190395.6572116271</v>
+        <v>184546.3061521451</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>222570.0306813615</v>
+        <v>211780.4059376684</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>261973.1416574971</v>
+        <v>243397.4952439234</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>310145.4989683788</v>
+        <v>279809.1263013253</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>368952.7996783586</v>
+        <v>321441.8233760892</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>440653.2876727466</v>
+        <v>368744.0654996811</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>527979.1376865178</v>
+        <v>422481.3287721419</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>634234.7400238817</v>
+        <v>483515.1285874736</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>763415.3593191212</v>
+        <v>552816.4657388779</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>920350.3608941813</v>
+        <v>631480.7741909469</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>1110876.066100348</v>
+        <v>720744.6256291682</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>1342044.344211867</v>
+        <v>822004.4638225622</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>1622374.309983057</v>
+        <v>936837.665863856</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>1962156.01751277</v>
+        <v>1067026.25732857</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>2373816.876405435</v>
+        <v>1214583.644381332</v>
       </c>
     </row>
     <row r="11">
@@ -1335,64 +1335,64 @@
         <v>75652.8</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>86107.07840485034</v>
+        <v>86110.92206963341</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>99260.93685037787</v>
+        <v>99161.81495436524</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>115669.9426799763</v>
+        <v>115177.8670543701</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>136016.8735994151</v>
+        <v>134560.8335079766</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>161136.2287516634</v>
+        <v>157736.2369827041</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>192044.3751482404</v>
+        <v>185148.2813756446</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>229976.3601266659</v>
+        <v>217255.9295614645</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>276430.6668455202</v>
+        <v>254530.9042475933</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>333223.4785411567</v>
+        <v>297458.405030431</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>402554.3591953223</v>
+        <v>346541.282791417</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>487085.665954327</v>
+        <v>402308.2719875161</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>590038.4968483469</v>
+        <v>465661.8308423641</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>715308.5635840928</v>
+        <v>537617.6431272305</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>867606.084318105</v>
+        <v>619320.4704498713</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>1052624.640403869</v>
+        <v>712061.7749339815</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>1277244.964236514</v>
+        <v>817299.4130516622</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>1549780.858713624</v>
+        <v>936679.7225045481</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>1880275.936127887</v>
+        <v>1072062.352377739</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>2280861.658118242</v>
+        <v>1225548.22213204</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>2766189.322086928</v>
+        <v>1399511.037426833</v>
       </c>
     </row>
     <row r="12">
@@ -1405,64 +1405,64 @@
         <v>167323.6</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>186645.4251768963</v>
+        <v>186652.5290851465</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>210956.5471939225</v>
+        <v>210773.348893705</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>241283.8724083048</v>
+        <v>240374.4122202347</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>278889.3189244689</v>
+        <v>276198.2478238308</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>325315.2182622381</v>
+        <v>319031.3119016553</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>382440.0323598674</v>
+        <v>369694.5875277898</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>452546.3908080274</v>
+        <v>429036.335499133</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>538403.8085030173</v>
+        <v>497928.3994915166</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>643368.9775095354</v>
+        <v>577267.5313317563</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>771507.1588736809</v>
+        <v>667983.1061675062</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>927738.9536270736</v>
+        <v>771052.3374871972</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>1118017.634534865</v>
+        <v>888143.1596145059</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>1349543.303607974</v>
+        <v>1021132.771714704</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>1631021.443637226</v>
+        <v>1172136.936188749</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>1972975.00129805</v>
+        <v>1343542.549124928</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>2388121.030336861</v>
+        <v>1538044.038680831</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>2891825.202925491</v>
+        <v>1758684.186327111</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>3502650.246110944</v>
+        <v>2008900.018241595</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>4243017.675631013</v>
+        <v>2292574.479460611</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>5140006.198492363</v>
+        <v>2614094.681808165</v>
       </c>
     </row>
     <row r="13">
@@ -1475,61 +1475,61 @@
         <v>-5.820766091346741e-11</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>-2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9" t="n">
         <v>-5.820766091346741e-11</v>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>1.164153218269348e-10</v>
-      </c>
       <c r="H13" s="9" t="n">
-        <v>5.820766091346741e-11</v>
+        <v>-5.820766091346741e-11</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>5.820766091346741e-11</v>
+        <v>-5.820766091346741e-11</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.164153218269348e-10</v>
+        <v>-2.328306436538696e-10</v>
       </c>
       <c r="K13" s="9" t="n">
+        <v>-1.164153218269348e-10</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>-1.164153218269348e-10</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>-3.492459654808044e-10</v>
+      </c>
+      <c r="N13" s="9" t="n">
         <v>3.492459654808044e-10</v>
       </c>
-      <c r="L13" s="9" t="n">
-        <v>1.164153218269348e-10</v>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>1.164153218269348e-10</v>
-      </c>
-      <c r="N13" s="9" t="n">
+      <c r="O13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="9" t="n">
-        <v>2.328306436538696e-10</v>
-      </c>
       <c r="P13" s="9" t="n">
-        <v>-4.656612873077393e-10</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>-4.656612873077393e-10</v>
+        <v>-6.984919309616089e-10</v>
       </c>
       <c r="R13" s="9" t="n">
-        <v>-9.313225746154785e-10</v>
+        <v>0</v>
       </c>
       <c r="S13" s="9" t="n">
-        <v>-9.313225746154785e-10</v>
+        <v>0</v>
       </c>
       <c r="T13" s="9" t="n">
         <v>-4.656612873077393e-10</v>
       </c>
       <c r="U13" s="9" t="n">
-        <v>-9.313225746154785e-10</v>
+        <v>4.656612873077393e-10</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>1.862645149230957e-09</v>
+        <v>4.656612873077393e-10</v>
       </c>
     </row>
   </sheetData>
@@ -1683,64 +1683,64 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>24347.30765580498</v>
+        <v>24355.80881125544</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>29611.92341296168</v>
+        <v>29440.18041609003</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>36150.9682592531</v>
+        <v>35467.1870120833</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>44208.87854643864</v>
+        <v>42486.37947910043</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>54088.43679815016</v>
+        <v>50543.00387040331</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>66161.1857942442</v>
+        <v>59676.75281016456</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>80880.43202764675</v>
+        <v>69922.17636389198</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>98797.26552822588</v>
+        <v>81310.93636410446</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>120580.1381727606</v>
+        <v>93875.98045163541</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>147038.6747477692</v>
+        <v>107657.5661127697</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>179152.545407998</v>
+        <v>122710.8986199299</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>218106.4106378993</v>
+        <v>139695.8621098253</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>265332.1671331053</v>
+        <v>158879.21696909</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>322559.9830918054</v>
+        <v>180558.7172652823</v>
       </c>
       <c r="P2" s="8" t="n">
-        <v>391879.923622039</v>
+        <v>205068.0442956473</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>475816.3425198153</v>
+        <v>232782.1509308253</v>
       </c>
       <c r="R2" s="8" t="n">
-        <v>577417.668963057</v>
+        <v>264123.1271015673</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>700364.7628104654</v>
+        <v>299566.6967890363</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>849101.6695902626</v>
+        <v>339649.4604637559</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>1028993.399290783</v>
+        <v>384977.0036447825</v>
       </c>
     </row>
     <row r="3">
@@ -1750,64 +1750,64 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>-2318.66936</v>
+        <v>-2320.413312000001</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>-2793.0413392</v>
+        <v>-2760.006177116161</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>-3364.628097824</v>
+        <v>-3238.74221163375</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-4053.38747614528</v>
+        <v>-3748.721251197387</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>-4883.382157057241</v>
+        <v>-4279.045357012842</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>-5883.625555001834</v>
+        <v>-4815.947732935925</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>-7089.102365172638</v>
+        <v>-5343.175637165725</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>-8541.999911195097</v>
+        <v>-5842.63873199966</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>-10293.1939224794</v>
+        <v>-6295.306753873037</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>-12404.04142241051</v>
+        <v>-6682.30965357735</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>-14948.5443397236</v>
+        <v>-6986.163277074304</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>-18015.96065972214</v>
+        <v>-7304.393968742251</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>-21713.95588317221</v>
+        <v>-7637.71196504048</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>-26172.40683144354</v>
+        <v>-7986.864129233592</v>
       </c>
       <c r="P3" s="8" t="n">
-        <v>-31547.99311912926</v>
+        <v>-8352.63591607839</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>-38029.73974705946</v>
+        <v>-8735.853445474848</v>
       </c>
       <c r="R3" s="8" t="n">
-        <v>-45845.70826147865</v>
+        <v>-9137.385691286567</v>
       </c>
       <c r="S3" s="8" t="n">
-        <v>-55271.07500308329</v>
+        <v>-9558.14679189671</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>-66637.88461265681</v>
+        <v>-9999.098489447146</v>
       </c>
       <c r="U3" s="8" t="n">
-        <v>-80346.82695811556</v>
+        <v>-10461.25270511278</v>
       </c>
     </row>
     <row r="4">
@@ -1817,64 +1817,64 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>-3800.334330876827</v>
+        <v>-3801.731578077044</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>-4781.684387785156</v>
+        <v>-4744.254395925717</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>-5964.994022050229</v>
+        <v>-5822.147668510639</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-7396.506684310861</v>
+        <v>-7046.086778567001</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>-9131.376079508931</v>
+        <v>-8424.711687041565</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>-11235.71472902245</v>
+        <v>-9964.813385654521</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-13789.01720131475</v>
+        <v>-11671.75705093855</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>-16887.04756120098</v>
+        <v>-13550.18113125213</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>-20645.29599037784</v>
+        <v>-15604.98473888651</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>-25203.12887570566</v>
+        <v>-17842.5844606131</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>-30728.78056902342</v>
+        <v>-20272.38948153941</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>-37425.36429161622</v>
+        <v>-23030.25568819749</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>-45538.11528744164</v>
+        <v>-26157.34277799932</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>-55363.12255510267</v>
+        <v>-29700.57306488751</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>-67257.85781788286</v>
+        <v>-33713.27505088675</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>-81653.87365978552</v>
+        <v>-38255.93633066627</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>-99072.11919065124</v>
+        <v>-43397.07351145458</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>-120141.4139019383</v>
+        <v>-49214.22944626872</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>-145620.7317984488</v>
+        <v>-55795.11062773475</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>-176426.0823825704</v>
+        <v>-63238.88016546929</v>
       </c>
     </row>
     <row r="5">
@@ -1887,61 +1887,61 @@
         <v>-772.3737519681163</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>5965.899935630296</v>
+        <v>5442.285515661788</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>12328.64125125037</v>
+        <v>10591.28860579486</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>18671.540497871</v>
+        <v>14822.53676944732</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>25313.72684472305</v>
+        <v>18207.41379029289</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>32557.380899126</v>
+        <v>20762.75511172297</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>40704.53859304514</v>
+        <v>22470.78338957136</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>50072.20744722441</v>
+        <v>23297.55061336177</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>61006.71978834717</v>
+        <v>23209.90681393276</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>73898.11688477488</v>
+        <v>22190.59965264413</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>89195.28011579858</v>
+        <v>20250.82619416714</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>107422.4910295098</v>
+        <v>18940.31115849665</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>129198.1054033255</v>
+        <v>18107.5125422586</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>155256.0636099259</v>
+        <v>17639.00474701554</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>186471.0291763623</v>
+        <v>17449.95871419617</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>223888.0496449734</v>
+        <v>17477.00239573891</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>268757.7705489723</v>
+        <v>17672.86649129976</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>322578.4078900195</v>
+        <v>18002.36915075011</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>387145.9018914632</v>
+        <v>18439.40491662902</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>464613.9415873359</v>
+        <v>18964.68686318066</v>
       </c>
     </row>
     <row r="6">
@@ -1954,61 +1954,61 @@
         <v>854.9315000000061</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>-6603.585074999995</v>
+        <v>-6024.00237899999</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>-13646.42924625</v>
+        <v>-11723.37386092199</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-20667.31046268749</v>
+        <v>-16406.89311595364</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-28019.46908061561</v>
+        <v>-20153.57402189227</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>-36037.38529078171</v>
+        <v>-22982.05153472256</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-45055.37914447027</v>
+        <v>-24872.64811947504</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>-55424.34257001347</v>
+        <v>-25787.78711919489</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>-67527.62678150306</v>
+        <v>-25690.77521955359</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>-81796.96391091886</v>
+        <v>-24562.51600807643</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>-98729.21552293893</v>
+        <v>-22415.40338508753</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>-118904.702749904</v>
+        <v>-20964.80957300703</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>-143007.8763916678</v>
+        <v>-20042.99449531434</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>-171851.1264888385</v>
+        <v>-19524.40867966718</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>-206402.6079007342</v>
+        <v>-19315.15583025906</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>-247819.071566477</v>
+        <v>-19345.09016602334</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>-297484.8424439693</v>
+        <v>-19561.88984957969</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>-357058.2783559109</v>
+        <v>-19926.61250124944</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>-428527.2845944538</v>
+        <v>-20410.36229456434</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>-514275.7544388652</v>
+        <v>-20991.79075629561</v>
       </c>
     </row>
     <row r="7">
@@ -2018,64 +2018,64 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>13543.19042080498</v>
+        <v>13549.94762425544</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>15508.04708419782</v>
+        <v>15368.50845619121</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>18059.73953053887</v>
+        <v>17516.71144199443</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>21271.58178779941</v>
+        <v>19932.9488139974</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>25243.50277877168</v>
+        <v>22547.05552483774</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>30104.58819987562</v>
+        <v>25278.81883059182</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>36016.87156902326</v>
+        <v>28038.13576789546</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>43180.44909210024</v>
+        <v>30726.80990352692</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>51840.05392669699</v>
+        <v>33241.87791155231</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>62293.28752148946</v>
+        <v>35480.22888435654</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>74900.77207470899</v>
+        <v>37344.14360824008</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>90098.56180722793</v>
+        <v>39215.76279796343</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>108413.2347975669</v>
+        <v>41114.81173073265</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>130480.1849338095</v>
+        <v>43057.11471769403</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>157065.7488520423</v>
+        <v>45055.62155018427</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>189093.9398557091</v>
+        <v>47121.17999002004</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>227678.7247720213</v>
+        <v>49263.1179359743</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>274162.9764436315</v>
+        <v>51489.68299851498</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>330165.4711585112</v>
+        <v>53808.37529029918</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>397637.5852708032</v>
+        <v>56226.20029694128</v>
       </c>
     </row>
     <row r="8">
@@ -2085,64 +2085,64 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>94001.70396492815</v>
+        <v>94007.06392117839</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>116038.9016509047</v>
+        <v>115942.9837642265</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>142860.2477902836</v>
+        <v>142349.2808961654</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>175619.2321762661</v>
+        <v>174040.8523455015</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>215692.9107378501</v>
+        <v>211880.0991718504</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>264734.75624807</v>
+        <v>256776.0908634245</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>324737.0687092294</v>
+        <v>309683.3345392122</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>398105.2867650592</v>
+        <v>371601.4510400648</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>487746.9350249625</v>
+        <v>443577.1399989407</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>597178.4394746155</v>
+        <v>526709.8119975199</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>730653.6599738663</v>
+        <v>622162.1578588361</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>893318.7456604273</v>
+        <v>731523.3703117218</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>1091398.841622919</v>
+        <v>856607.5325377719</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>1332423.295328178</v>
+        <v>999478.812608933</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>1625497.368013205</v>
+        <v>1162480.945937615</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>1981630.097126175</v>
+        <v>1348271.307092299</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>2414129.938637102</v>
+        <v>1559859.974991126</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>2939082.212542546</v>
+        <v>1800654.295541997</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>3575925.265721703</v>
+        <v>2074509.546888571</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>4348145.755671801</v>
+        <v>2385786.417662771</v>
       </c>
     </row>
   </sheetData>
@@ -2296,64 +2296,64 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>80502.49816</v>
+        <v>80546.09696</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>96868.950472</v>
+        <v>95682.499193344</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>116567.202836</v>
+        <v>112133.5339768776</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>140276.487372112</v>
+        <v>129620.0867262457</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>168814.714488607</v>
+        <v>147760.8689123304</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>203166.831549657</v>
+        <v>166077.5965088486</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>244518.9903388493</v>
+        <v>184008.9000458804</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>294299.7152313175</v>
+        <v>200933.2742190017</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>354229.509003713</v>
+        <v>216200.4207920049</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>426380.6286903365</v>
+        <v>229169.2873935428</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>513249.1202491786</v>
+        <v>239250.0898231309</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>617841.6306003595</v>
+        <v>249789.6974306805</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>743780.0340080727</v>
+        <v>260809.8412666213</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>895427.5351006094</v>
+        <v>272333.3270570734</v>
       </c>
       <c r="P2" s="8" t="n">
-        <v>1078040.665155656</v>
+        <v>284384.0906812427</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>1297952.498289396</v>
+        <v>296987.2566273254</v>
       </c>
       <c r="R2" s="8" t="n">
-        <v>1562793.512072458</v>
+        <v>310169.1995922365</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>1881757.841719673</v>
+        <v>323957.6093998931</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>2265924.275287529</v>
+        <v>338381.5594227531</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>2728643.265918219</v>
+        <v>353471.5787018567</v>
       </c>
     </row>
     <row r="3">
@@ -2363,64 +2363,64 @@
         </is>
       </c>
       <c r="B3" s="10" t="n">
-        <v>0.316306164450336</v>
+        <v>0.3163076798254644</v>
       </c>
       <c r="C3" s="10" t="n">
-        <v>0.3163138506187497</v>
+        <v>0.3163169182970363</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>0.3163216217448344</v>
+        <v>0.3163262789002158</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.3163294781657683</v>
+        <v>0.3163357622011241</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.3163374202026129</v>
+        <v>0.3163453687320789</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>0.31634544815982</v>
+        <v>0.3163550989903721</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>0.3163535623247366</v>
+        <v>0.3163649534370487</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>0.3163617629671086</v>
+        <v>0.3163749324956791</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.3163700503385846</v>
+        <v>0.3163850365511335</v>
       </c>
       <c r="K3" s="10" t="n">
-        <v>0.3163784246722187</v>
+        <v>0.3163952659483569</v>
       </c>
       <c r="L3" s="10" t="n">
-        <v>0.3163868861819739</v>
+        <v>0.3164056209911482</v>
       </c>
       <c r="M3" s="10" t="n">
-        <v>0.3163954350622263</v>
+        <v>0.3164161019409424</v>
       </c>
       <c r="N3" s="10" t="n">
-        <v>0.316404071487271</v>
+        <v>0.316426709015601</v>
       </c>
       <c r="O3" s="10" t="n">
-        <v>0.3164127956108282</v>
+        <v>0.3164374423882104</v>
       </c>
       <c r="P3" s="10" t="n">
-        <v>0.316421607565553</v>
+        <v>0.3164483021858915</v>
       </c>
       <c r="Q3" s="10" t="n">
-        <v>0.3164305074625486</v>
+        <v>0.3164592884886203</v>
       </c>
       <c r="R3" s="10" t="n">
-        <v>0.3164394953908803</v>
+        <v>0.3164704013280668</v>
       </c>
       <c r="S3" s="10" t="n">
-        <v>0.3164485714170964</v>
+        <v>0.3164816406864467</v>
       </c>
       <c r="T3" s="10" t="n">
-        <v>0.3164577355847517</v>
+        <v>0.3164930064953954</v>
       </c>
       <c r="U3" s="10" t="n">
-        <v>0.316466987913937</v>
+        <v>0.3165044986348611</v>
       </c>
     </row>
     <row r="4">
@@ -2430,64 +2430,64 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>0.2346008002927391</v>
+        <v>0.2346099989937993</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.2368610285719238</v>
+        <v>0.2367157990725232</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.2387183788198176</v>
+        <v>0.2383273435270836</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.2402448369002489</v>
+        <v>0.2395607693625308</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.2414995379892343</v>
+        <v>0.2405008193003875</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>0.2425310590634472</v>
+        <v>0.2412094604028764</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>0.2433793026878711</v>
+        <v>0.2417319264298251</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>0.2440770449202446</v>
+        <v>0.2421009599497582</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.2446512071836265</v>
+        <v>0.2423397795504088</v>
       </c>
       <c r="K4" s="10" t="n">
-        <v>0.2451239012997197</v>
+        <v>0.2424641272203436</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>0.2455132881140143</v>
+        <v>0.2424836333252141</v>
       </c>
       <c r="M4" s="10" t="n">
-        <v>0.2458342829418592</v>
+        <v>0.2425026923887784</v>
       </c>
       <c r="N4" s="10" t="n">
-        <v>0.2460991351447717</v>
+        <v>0.2425213333619918</v>
       </c>
       <c r="O4" s="10" t="n">
-        <v>0.2463179042804989</v>
+        <v>0.2425395836868875</v>
       </c>
       <c r="P4" s="10" t="n">
-        <v>0.2464988512710131</v>
+        <v>0.2425574693700679</v>
       </c>
       <c r="Q4" s="10" t="n">
-        <v>0.2466487597455195</v>
+        <v>0.2425750150524477</v>
       </c>
       <c r="R4" s="10" t="n">
-        <v>0.2467732000139287</v>
+        <v>0.2425922440754454</v>
       </c>
       <c r="S4" s="10" t="n">
-        <v>0.246876745905884</v>
+        <v>0.2426091785437974</v>
       </c>
       <c r="T4" s="10" t="n">
-        <v>0.2469631528856157</v>
+        <v>0.2426258393851708</v>
       </c>
       <c r="U4" s="10" t="n">
-        <v>0.2470355043532487</v>
+        <v>0.2426422464067382</v>
       </c>
     </row>
     <row r="5">
@@ -2497,64 +2497,64 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>23122.05950777309</v>
+        <v>23130.56066322355</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>29092.80640481138</v>
+        <v>28865.07420448423</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>36292.31923643257</v>
+        <v>35423.21099504035</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>45001.95320047493</v>
+        <v>42869.92238216312</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>55557.27541727814</v>
+        <v>51257.77576486601</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>68360.5288266518</v>
+        <v>60628.08901178896</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>83895.37564947472</v>
+        <v>71013.50502228174</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>102744.4652561909</v>
+        <v>82442.24512363585</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>125610.464996896</v>
+        <v>94944.11657912612</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>153341.3102398511</v>
+        <v>108558.159296363</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>186960.5753224161</v>
+        <v>123341.6208012305</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>227704.0451994073</v>
+        <v>140121.0778155063</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>277063.7843605513</v>
+        <v>159146.9548781974</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>336841.2625843545</v>
+        <v>180704.7375389325</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>409211.4154787064</v>
+        <v>205118.887987066</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>496799.9026985973</v>
+        <v>232757.4258865683</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>602776.2917792804</v>
+        <v>264037.2211577346</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>730966.4570873907</v>
+        <v>299430.0613607529</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>885988.1613185176</v>
+        <v>339469.5718467511</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>1073414.605243922</v>
+        <v>384759.0825130233</v>
       </c>
     </row>
     <row r="6">
@@ -2564,64 +2564,64 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>12667.78110292276</v>
+        <v>12672.43859359015</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>15938.94795928385</v>
+        <v>15814.18131975239</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>19883.3134068341</v>
+        <v>19407.15889503546</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>24655.0222810362</v>
+        <v>23486.95592855667</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>30437.92026502977</v>
+        <v>28082.37229013855</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>37452.38243007485</v>
+        <v>33216.04461884841</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>45963.39067104919</v>
+        <v>38905.85683646183</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>56290.15853733661</v>
+        <v>45167.27043750712</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>68817.65330125947</v>
+        <v>52016.61579628835</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>84010.42958568553</v>
+        <v>59475.281535377</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>102429.2685634114</v>
+        <v>67574.63160513135</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>124751.2143053874</v>
+        <v>76767.51896065829</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>151793.7176248055</v>
+        <v>87191.14259333107</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>184543.7418503422</v>
+        <v>99001.91021629171</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>224192.8593929429</v>
+        <v>112377.5835029558</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>272179.5788659517</v>
+        <v>127519.7877688876</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>330240.3973021708</v>
+        <v>144656.9117048486</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>400471.3796731276</v>
+        <v>164047.4314875624</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>485402.4393281628</v>
+        <v>185983.7020924492</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>588086.9412752348</v>
+        <v>210796.267218231</v>
       </c>
     </row>
     <row r="7">
@@ -2631,64 +2631,64 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>6.147457230769553</v>
+        <v>6.149717431229907</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7.73489848672487</v>
+        <v>7.674351373215817</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>9.64903149031346</v>
+        <v>9.417961859986118</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>11.96466009042189</v>
+        <v>11.39781749295135</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>14.77100144868089</v>
+        <v>13.62789435573241</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>18.17499981320242</v>
+        <v>16.11917762161136</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>22.30524635969865</v>
+        <v>18.88034605155986</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>27.31664995708479</v>
+        <v>21.91890284409109</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>33.39602862997145</v>
+        <v>25.24277285019364</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>40.76882278123843</v>
+        <v>28.86233560211667</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>49.70716991054557</v>
+        <v>32.79281148785466</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>60.53962791099961</v>
+        <v>37.25396229131661</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>73.66289166322137</v>
+        <v>42.31236833345371</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>89.55591756865817</v>
+        <v>48.04393159893802</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>108.7969553124076</v>
+        <v>54.53491678367119</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>132.0840884897559</v>
+        <v>61.88316920041958</v>
       </c>
       <c r="R7" s="9" t="n">
-        <v>160.2600093728363</v>
+        <v>70.19952196960431</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>194.3419023967672</v>
+        <v>79.6094091533291</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>235.5574911846729</v>
+        <v>90.2547056145235</v>
       </c>
       <c r="U7" s="9" t="n">
-        <v>285.3885214853823</v>
+        <v>102.2958185495453</v>
       </c>
     </row>
     <row r="8">
@@ -2701,61 +2701,61 @@
         <v>49732.59775999999</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>75979.88837866664</v>
+        <v>73874.83348117329</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>104759.8419432889</v>
+        <v>97468.28262085484</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>137031.7902393541</v>
+        <v>120250.5793517932</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>173871.464876731</v>
+        <v>141814.3384822201</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>216506.8550099991</v>
+        <v>161632.8063075884</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>266359.140310267</v>
+        <v>179095.8546815405</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>325090.0636208772</v>
+        <v>193555.591127702</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>394657.3223855167</v>
+        <v>204379.4388369729</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>477379.8252296733</v>
+        <v>211007.1581204748</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>576014.988914819</v>
+        <v>213007.1415718323</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>693850.6522304586</v>
+        <v>216160.5081734876</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>834814.670620447</v>
+        <v>220334.4959494121</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>1003605.844697784</v>
+        <v>225420.8486615428</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>1205850.546931713</v>
+        <v>231331.8266697997</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>1448290.267396699</v>
+        <v>237996.8864547543</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>1739006.330108242</v>
+        <v>245359.9175114135</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>2087689.27049006</v>
+        <v>253376.9438772607</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>2505961.853221547</v>
+        <v>262014.2130201767</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>3007766.497727085</v>
+        <v>271246.6076975051</v>
       </c>
     </row>
     <row r="9">
@@ -2768,61 +2768,61 @@
         <v>491395.3736</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>508170.5929866667</v>
+        <v>506854.9336757333</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>541884.8321395555</v>
+        <v>536094.1769590343</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>593661.8990304295</v>
+        <v>577744.9029939654</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>665227.6958889846</v>
+        <v>630269.8081082301</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>758967.7492771724</v>
+        <v>691898.4490437085</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>878006.727641266</v>
+        <v>760589.7051544396</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>1026312.596926735</v>
+        <v>834025.0930371007</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>1208828.886109762</v>
+        <v>909635.6739953901</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>1431639.471496448</v>
+        <v>984662.9181959749</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>1702171.372599682</v>
+        <v>1056250.949291122</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>2029442.319456238</v>
+        <v>1125335.582568856</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>2424361.343628003</v>
+        <v>1192711.168626686</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>2900092.412587367</v>
+        <v>1259054.751000982</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>3472493.228632978</v>
+        <v>1324946.220732045</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>4160643.818966353</v>
+        <v>1390885.135970514</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>4987482.536598608</v>
+        <v>1457304.76341699</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>5980570.672117482</v>
+        <v>1524583.805626716</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>7173011.163373607</v>
+        <v>1593056.200912657</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>8604552.026742186</v>
+        <v>1663019.318166556</v>
       </c>
     </row>
     <row r="10">
@@ -2835,61 +2835,61 @@
         <v>9.959931511477237</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>8.583285771859192</v>
+        <v>8.676753597605037</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>7.627281786013327</v>
+        <v>7.857272829341495</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>6.963390129175921</v>
+        <v>7.350457775854668</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>6.502354256372167</v>
+        <v>7.058727828531886</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>6.182190455814006</v>
+        <v>6.918696300990987</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>5.95985448320417</v>
+        <v>6.889112546037882</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>5.805454502225119</v>
+        <v>6.943254094698132</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>5.698232293211889</v>
+        <v>7.064096777594941</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>5.623772425841589</v>
+        <v>7.241237987369744</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>5.572064184612215</v>
+        <v>7.468940695007808</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>5.536155683758483</v>
+        <v>7.651394787666513</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>5.51121922483228</v>
+        <v>7.797591977296887</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>5.493902239466861</v>
+        <v>7.914737161295583</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>5.481876555185321</v>
+        <v>8.00860349462787</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>5.473525385545361</v>
+        <v>8.083816902746689</v>
       </c>
       <c r="R10" s="9" t="n">
-        <v>5.467725962184279</v>
+        <v>8.144084056688051</v>
       </c>
       <c r="S10" s="9" t="n">
-        <v>5.463698584850193</v>
+        <v>8.192375045423118</v>
       </c>
       <c r="T10" s="9" t="n">
-        <v>5.460901795034857</v>
+        <v>8.231069747935191</v>
       </c>
       <c r="U10" s="9" t="n">
-        <v>5.458959579885319</v>
+        <v>8.262075118537812</v>
       </c>
     </row>
   </sheetData>
@@ -3057,13 +3057,13 @@
     </row>
     <row r="2">
       <c r="A2" s="20" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>156.0838105097744</v>
+        <v>70.16479609998046</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>237.8217269820379</v>
+        <v>97.0097244573295</v>
       </c>
       <c r="D2" s="10">
         <f>B2/'Summary'!$B$2-1</f>
@@ -3072,13 +3072,13 @@
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>105.9103422088017</v>
+        <v>63.76257054983443</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>153.406106835808</v>
+        <v>87.29699363888786</v>
       </c>
       <c r="D3" s="10">
         <f>B3/'Summary'!$B$2-1</f>
@@ -3087,13 +3087,13 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
-        <v>0.28</v>
+        <v>0.2849</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>80.87409058419072</v>
+        <v>57.32583665473236</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>112.1456638392772</v>
+        <v>77.58016581124872</v>
       </c>
       <c r="D4" s="10">
         <f>B4/'Summary'!$B$2-1</f>
@@ -3105,10 +3105,10 @@
         <v>0.3157</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>57.75526827071646</v>
+        <v>52.41009407163257</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>75.17953446617932</v>
+        <v>70.19772724656579</v>
       </c>
       <c r="D5" s="10">
         <f>B5/'Summary'!$B$2-1</f>
@@ -3120,10 +3120,10 @@
         <v>0.3237</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>54.41105716024056</v>
+        <v>51.23655514421238</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>69.98160596090575</v>
+        <v>68.44086712244061</v>
       </c>
       <c r="D6" s="10">
         <f>B6/'Summary'!$B$2-1</f>
@@ -3135,10 +3135,10 @@
         <v>0.3579</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>43.94753340268149</v>
+        <v>46.64455562171646</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>54.09019265766425</v>
+        <v>61.58950989620313</v>
       </c>
       <c r="D7" s="10">
         <f>B7/'Summary'!$B$2-1</f>
@@ -3150,10 +3150,10 @@
         <v>0.4</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>35.99240529135729</v>
+        <v>41.81648289180088</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>42.5113807850869</v>
+        <v>54.43119936604813</v>
       </c>
       <c r="D8" s="10">
         <f>B8/'Summary'!$B$2-1</f>
@@ -3177,7 +3177,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>43.93936943614966</v>
+        <v>46.64029756780567</v>
       </c>
     </row>
     <row r="12">
@@ -3185,7 +3185,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>43.93936943614966</v>
+        <v>46.64029756780567</v>
       </c>
     </row>
     <row r="13">
@@ -3193,7 +3193,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>43.93936943614966</v>
+        <v>46.64029756780567</v>
       </c>
     </row>
     <row r="14">
@@ -3201,7 +3201,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>43.93936943614966</v>
+        <v>46.64029756780567</v>
       </c>
     </row>
     <row r="15">
@@ -3209,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>43.93936943614966</v>
+        <v>46.64029756780567</v>
       </c>
     </row>
     <row r="16">
@@ -3217,7 +3217,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>43.93936943614966</v>
+        <v>46.64029756780567</v>
       </c>
     </row>
   </sheetData>
@@ -3680,17 +3680,17 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>78902.72859820566</v>
+        <v>96360.51181116889</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>90543.82859820565</v>
+        <v>108001.6118111689</v>
       </c>
       <c r="D7" s="9">
         <f>C7/$B$3</f>
         <v/>
       </c>
       <c r="E7" s="9" t="n">
-        <v>44.18664184956641</v>
+        <v>48.82813681143778</v>
       </c>
       <c r="F7" s="10">
         <f>D7/$B$2-1</f>
@@ -3704,17 +3704,17 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>99795.05149032849</v>
+        <v>133015.9368125314</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>111436.1514903285</v>
+        <v>144657.0368125314</v>
       </c>
       <c r="D8" s="9">
         <f>C8/$B$3</f>
         <v/>
       </c>
       <c r="E8" s="9" t="n">
-        <v>49.74127672288594</v>
+        <v>58.57370235052318</v>
       </c>
       <c r="F8" s="10">
         <f>D8/$B$2-1</f>
@@ -3728,17 +3728,17 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>100442.1462520464</v>
+        <v>106490.7945082575</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>112083.2462520464</v>
+        <v>118131.8945082575</v>
       </c>
       <c r="D9" s="9">
         <f>C9/$B$3</f>
         <v/>
       </c>
       <c r="E9" s="9" t="n">
-        <v>49.91331958994005</v>
+        <v>51.52147167115555</v>
       </c>
       <c r="F9" s="10">
         <f>D9/$B$2-1</f>
@@ -3752,17 +3752,17 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>132506.2759098136</v>
+        <v>148229.5677143865</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>144147.3759098136</v>
+        <v>159870.6677143865</v>
       </c>
       <c r="D10" s="9">
         <f>C10/$B$3</f>
         <v/>
       </c>
       <c r="E10" s="9" t="n">
-        <v>58.43819897742189</v>
+        <v>62.61854529085117</v>
       </c>
       <c r="F10" s="10">
         <f>D10/$B$2-1</f>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.2652836941995044</v>
+        <v>0.1558113694332027</v>
       </c>
     </row>
     <row r="16">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.2907215393505239</v>
+        <v>0.2177365969170268</v>
       </c>
     </row>
     <row r="17">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>43.93936943614966</v>
+        <v>52.4113326611044</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>69.95225297418403</v>
+        <v>77.58249722218574</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4139,73 +4139,103 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Annual contracted sales, EGP mn</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>382200</v>
+          <t>Delivery growth, real, slower reading</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>FY2025 as reported, held flat in nominal terms</t>
+          <t>it scales with prices and no more</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Share of contracted sales that enters the order book</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>0.481</v>
+          <t>Delivery growth, real, faster reading</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>0.07099999999999999</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>measured on the company's own two disclosed series; FY2025 was 48.1%</t>
+          <t>its own 2019-2025 real rate</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Long-run growth</t>
+          <t>Long-run real growth</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>below Egypt's own nominal growth</t>
+          <t>in the converged state, beside a converged discount rate</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>0.225</v>
+          <t>Share of contracted sales that enters the order book</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0.481</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Egypt's statutory corporate rate</t>
+          <t>measured on the company's own two disclosed series; FY2025 was 48.1%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>Long-run nominal growth</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>0.06079999999999997</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>4% terminal inflation compounded with 2% real</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Egypt's statutory corporate rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>Dividend payout</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B19" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>the company's recent behaviour</t>
         </is>
@@ -4248,7 +4278,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>72255.83250671037</v>
+        <v>85360.87492776931</v>
       </c>
     </row>
     <row r="3">
@@ -4268,7 +4298,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>6646.896091495293</v>
+        <v>10999.63688339958</v>
       </c>
     </row>
     <row r="5">
@@ -5037,64 +5067,64 @@
         </is>
       </c>
       <c r="B2" s="8" t="n">
-        <v>80502.49816</v>
+        <v>80546.09696</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>96868.950472</v>
+        <v>95682.499193344</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>116567.202836</v>
+        <v>112133.5339768776</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>140276.487372112</v>
+        <v>129620.0867262457</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>168814.714488607</v>
+        <v>147760.8689123304</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>203166.831549657</v>
+        <v>166077.5965088486</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>244518.9903388493</v>
+        <v>184008.9000458804</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>294299.7152313175</v>
+        <v>200933.2742190017</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>354229.509003713</v>
+        <v>216200.4207920049</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>426380.6286903365</v>
+        <v>229169.2873935428</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>513249.1202491786</v>
+        <v>239250.0898231309</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>617841.6306003595</v>
+        <v>249789.6974306805</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>743780.0340080727</v>
+        <v>260809.8412666213</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>895427.5351006094</v>
+        <v>272333.3270570734</v>
       </c>
       <c r="P2" s="8" t="n">
-        <v>1078040.665155656</v>
+        <v>284384.0906812427</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>1297952.498289396</v>
+        <v>296987.2566273254</v>
       </c>
       <c r="R2" s="8" t="n">
-        <v>1562793.512072458</v>
+        <v>310169.1995922365</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>1881757.841719673</v>
+        <v>323957.6093998931</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>2265924.275287529</v>
+        <v>338381.5594227531</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>2728643.265918219</v>
+        <v>353471.5787018567</v>
       </c>
     </row>
     <row r="3">
@@ -5104,64 +5134,64 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>55039.06173834017</v>
+        <v>55068.7479115855</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>66227.95974280473</v>
+        <v>65416.50591354676</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>79694.47619265741</v>
+        <v>76662.75043404101</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>95902.89932276482</v>
+        <v>88616.61779512296</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>115412.3032150404</v>
+        <v>101017.4023520869</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>138895.9291718701</v>
+        <v>113538.1020252087</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>167164.5366891065</v>
+        <v>125794.9329508629</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>201194.5384800199</v>
+        <v>137363.0231518293</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>242161.9014087962</v>
+        <v>147797.842757356</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>291482.9970745377</v>
+        <v>156661.2097614674</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>350863.8292579035</v>
+        <v>163550.0165804552</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>422359.3590870035</v>
+        <v>170752.2150646572</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>508445.0029569776</v>
+        <v>178282.641515743</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>612102.8054525126</v>
+        <v>186156.8655660611</v>
       </c>
       <c r="P3" s="8" t="n">
-        <v>736925.3048660655</v>
+        <v>194391.2280164848</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>887240.7305933998</v>
+        <v>203002.8807048547</v>
       </c>
       <c r="R3" s="8" t="n">
-        <v>1068263.921712108</v>
+        <v>212009.8285176762</v>
       </c>
       <c r="S3" s="8" t="n">
-        <v>1286278.260954564</v>
+        <v>221430.9736641559</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>1548855.010123518</v>
+        <v>231286.1623384457</v>
       </c>
       <c r="U3" s="8" t="n">
-        <v>1865117.750461433</v>
+        <v>241596.2339031527</v>
       </c>
     </row>
     <row r="4">
@@ -5171,64 +5201,64 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>25463.43642165983</v>
+        <v>25477.34904841449</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>30640.99072919527</v>
+        <v>30265.99327979724</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>36872.72664334257</v>
+        <v>35470.78354283661</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>44373.58804934718</v>
+        <v>41003.46893112274</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>53402.4112735666</v>
+        <v>46743.46656024354</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>64270.9023777869</v>
+        <v>52539.49448363986</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>77354.45364974285</v>
+        <v>58213.96709501751</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>93105.17675129764</v>
+        <v>63570.25106717244</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>112067.6075949168</v>
+        <v>68402.5780346489</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>134897.6316157989</v>
+        <v>72508.07763207541</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>162385.2909912751</v>
+        <v>75700.07324267572</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>195482.2715133561</v>
+        <v>79037.48236602338</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>235335.0310510951</v>
+        <v>82527.19975087827</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>283324.7296480968</v>
+        <v>86176.46149101231</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>341115.3602895909</v>
+        <v>89992.86266475785</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>410711.7676959964</v>
+        <v>93984.3759224707</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>494529.5903603502</v>
+        <v>98159.37107456036</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>595479.580765109</v>
+        <v>102526.6357357372</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>717069.2651640109</v>
+        <v>107095.3970843074</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>863525.5154567866</v>
+        <v>111875.344798704</v>
       </c>
     </row>
     <row r="5">
@@ -5238,64 +5268,64 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>5434.795527759074</v>
+        <v>5437.738921674436</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>6539.709336194602</v>
+        <v>6459.610951044766</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>7869.555940951652</v>
+        <v>7570.234997653327</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>9470.190908914105</v>
+        <v>8750.76778670173</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>11396.83210201891</v>
+        <v>9975.468189154244</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>13715.97419623551</v>
+        <v>11212.04682335868</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>16507.69535753426</v>
+        <v>12422.60513517979</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>19868.43654194412</v>
+        <v>13565.18474660238</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>23914.35042807461</v>
+        <v>14595.8834430787</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>28785.33693853437</v>
+        <v>15471.42320665294</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>34649.90636455193</v>
+        <v>16151.98717935921</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>41711.04012420138</v>
+        <v>16863.52549927569</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>50213.2541828633</v>
+        <v>17607.50524901955</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>60451.11238069835</v>
+        <v>18385.46606352335</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>72779.48783757816</v>
+        <v>19199.02387536353</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>87625.93204159674</v>
+        <v>20049.8748611707</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>105505.5853464497</v>
+        <v>20939.79960028235</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>127039.1520295107</v>
+        <v>21870.66745743409</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>152974.5709642134</v>
+        <v>22844.44120195883</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>184213.1431621929</v>
+        <v>23863.18187667519</v>
       </c>
     </row>
     <row r="6">
@@ -5308,61 +5338,61 @@
         <v>1142.6904</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1156.80214752</v>
+        <v>1156.823074944</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1176.43701782016</v>
+        <v>1176.061272170066</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1202.695310780206</v>
+        <v>1200.81344344363</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1236.903616764587</v>
+        <v>1231.388337136675</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1280.661359248099</v>
+        <v>1267.960221375189</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1335.896929597144</v>
+        <v>1310.536071513918</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>1404.93539482405</v>
+        <v>1358.92774630174</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1490.580169020502</v>
+        <v>1412.732278130115</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1596.211534062009</v>
+        <v>1471.32317183903</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>1725.905492722191</v>
+        <v>1533.85500961989</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>1884.577158886208</v>
+        <v>1599.282708829343</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>2078.153760896239</v>
+        <v>1667.744043948298</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>2313.78338636355</v>
+        <v>1739.383659001403</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>2600.08686770451</v>
+        <v>1814.35342464419</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>2947.461742721607</v>
+        <v>1892.8128145414</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>3368.449078773661</v>
+        <v>1974.929302112602</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>3878.176188966121</v>
+        <v>2060.878778782689</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>4494.890974735527</v>
+        <v>2150.845994940057</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>5240.606898390583</v>
+        <v>2245.025024874142</v>
       </c>
     </row>
     <row r="7">
@@ -5372,64 +5402,64 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>18885.95049390076</v>
+        <v>18896.91972674006</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>22944.47924548067</v>
+        <v>22649.55925380848</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>27826.73368457076</v>
+        <v>26724.48727301322</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>33700.70182965287</v>
+        <v>31051.88770097738</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>40768.6755547831</v>
+        <v>35536.61003395262</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>49274.26682230329</v>
+        <v>40059.48743890599</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>59510.86136261145</v>
+        <v>44480.8258883238</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>71831.80481452947</v>
+        <v>48646.13857426833</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>86662.67699782166</v>
+        <v>52393.96231344009</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>104516.0831432025</v>
+        <v>55565.33125358343</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>126009.479134001</v>
+        <v>58014.23105369662</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>151886.6542302685</v>
+        <v>60574.67415791834</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>183043.6231073356</v>
+        <v>63251.95045791042</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>220559.8338810349</v>
+        <v>66051.61176848755</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>265735.7855843082</v>
+        <v>68979.48536475014</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>320138.3739116781</v>
+        <v>72041.68824675861</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>385655.5559351268</v>
+        <v>75244.6421721654</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>464562.2525466323</v>
+        <v>78595.08949952044</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>559599.803225062</v>
+        <v>82100.1098874085</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>674071.7653962031</v>
+        <v>85767.13789715467</v>
       </c>
     </row>
     <row r="8">
@@ -5439,64 +5469,64 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>13543.19042080498</v>
+        <v>13549.94762425544</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>15508.04708419782</v>
+        <v>15368.50845619121</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>18059.73953053887</v>
+        <v>17516.71144199443</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>21271.58178779941</v>
+        <v>19932.9488139974</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>25243.50277877168</v>
+        <v>22547.05552483774</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>30104.58819987562</v>
+        <v>25278.81883059182</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>36016.87156902326</v>
+        <v>28038.13576789546</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>43180.44909210024</v>
+        <v>30726.80990352692</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>51840.05392669699</v>
+        <v>33241.87791155231</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>62293.28752148946</v>
+        <v>35480.22888435654</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>74900.77207470899</v>
+        <v>37344.14360824008</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>90098.56180722793</v>
+        <v>39215.76279796343</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>108413.2347975669</v>
+        <v>41114.81173073265</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>130480.1849338095</v>
+        <v>43057.11471769403</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>157065.7488520423</v>
+        <v>45055.62155018427</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>189093.9398557091</v>
+        <v>47121.17999002004</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>227678.7247720213</v>
+        <v>49263.1179359743</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>274162.9764436315</v>
+        <v>51489.68299851498</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>330165.4711585112</v>
+        <v>53808.37529029918</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>397637.5852708032</v>
+        <v>56226.20029694128</v>
       </c>
     </row>
     <row r="9">
@@ -5701,7 +5731,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>6646.896091495293</v>
+        <v>10999.63688339958</v>
       </c>
     </row>
     <row r="15">
@@ -5896,61 +5926,61 @@
         <v>49337.22416</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>59204.66899199999</v>
+        <v>58415.27340543999</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>71045.60279039999</v>
+        <v>68229.0393375539</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>85254.72334847999</v>
+        <v>78599.85331686211</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>102305.668018176</v>
+        <v>89289.43336795537</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>122766.8016218112</v>
+        <v>100004.16537211</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>147320.1619461734</v>
+        <v>110404.5985708095</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>176784.1943354081</v>
+        <v>120120.2032450407</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>212141.0332024897</v>
+        <v>128768.8578786837</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>254569.2398429876</v>
+        <v>135979.91391989</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>305483.0878115851</v>
+        <v>141419.1104766855</v>
       </c>
       <c r="P2" s="8" t="n">
-        <v>366579.7053739021</v>
+        <v>147075.874895753</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>439895.6464486825</v>
+        <v>152958.9098915831</v>
       </c>
       <c r="R2" s="8" t="n">
-        <v>527874.775738419</v>
+        <v>159077.2662872464</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>633449.7308861028</v>
+        <v>165440.3569387363</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>760139.6770633233</v>
+        <v>172057.9712162857</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>912167.612475988</v>
+        <v>178940.2900649371</v>
       </c>
       <c r="V2" s="8" t="n">
-        <v>1094601.134971186</v>
+        <v>186097.9016675346</v>
       </c>
       <c r="W2" s="8" t="n">
-        <v>1313521.361965423</v>
+        <v>193541.817734236</v>
       </c>
       <c r="X2" s="8" t="n">
-        <v>1576225.634358507</v>
+        <v>201283.4904436055</v>
       </c>
     </row>
     <row r="3">
@@ -5972,61 +6002,61 @@
         <v>17867.64</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>21441.168</v>
+        <v>21155.28576000001</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>25729.4016</v>
+        <v>24709.37376768001</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>30875.28192</v>
+        <v>28465.19858036738</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>37050.33830399999</v>
+        <v>32336.46558729735</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>44460.40596479999</v>
+        <v>36216.84145777303</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>53352.48715775999</v>
+        <v>39983.39296938143</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>64022.98458931198</v>
+        <v>43501.931550687</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>76827.58150717439</v>
+        <v>46634.07062233646</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>92193.09780860925</v>
+        <v>49245.57857718731</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>110631.7173703311</v>
+        <v>51215.4017202748</v>
       </c>
       <c r="P3" s="8" t="n">
-        <v>132758.0608443973</v>
+        <v>53264.0177890858</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>159309.6730132768</v>
+        <v>55394.57850064923</v>
       </c>
       <c r="R3" s="8" t="n">
-        <v>191171.6076159321</v>
+        <v>57610.3616406752</v>
       </c>
       <c r="S3" s="8" t="n">
-        <v>229405.9291391185</v>
+        <v>59914.77610630221</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>275287.1149669422</v>
+        <v>62311.3671505543</v>
       </c>
       <c r="U3" s="8" t="n">
-        <v>330344.5379603306</v>
+        <v>64803.82183657648</v>
       </c>
       <c r="V3" s="8" t="n">
-        <v>396413.4455523968</v>
+        <v>67395.97471003953</v>
       </c>
       <c r="W3" s="8" t="n">
-        <v>475696.1346628761</v>
+        <v>70091.81369844111</v>
       </c>
       <c r="X3" s="8" t="n">
-        <v>570835.3615954514</v>
+        <v>72895.48624637876</v>
       </c>
     </row>
     <row r="4">
@@ -6045,64 +6075,64 @@
         <v>10899.7</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>13297.634</v>
+        <v>13341.2328</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>16223.11348</v>
+        <v>16111.940027904</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>19792.1984456</v>
+        <v>19195.12087164371</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>24146.482103632</v>
+        <v>22555.03482901623</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>29458.70816643104</v>
+        <v>26134.96995707769</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>35939.62396304587</v>
+        <v>29856.58967896556</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>43846.34123491596</v>
+        <v>33620.90850568953</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>53492.53630659747</v>
+        <v>37311.13942327402</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>65260.89429404891</v>
+        <v>40797.49229098475</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>79618.29103873967</v>
+        <v>43943.79489646549</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>97134.31506726239</v>
+        <v>46615.57762617059</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>118503.8643820601</v>
+        <v>49449.80474584176</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>144574.7145461133</v>
+        <v>52456.35287438894</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>176381.1517462583</v>
+        <v>55645.69912915178</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>215185.0051304351</v>
+        <v>59028.95763620421</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>262525.7062591308</v>
+        <v>62617.91826048543</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>320281.3616361396</v>
+        <v>66425.08769072294</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>390743.2611960902</v>
+        <v>70463.73302231889</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>476706.7786592301</v>
+        <v>74747.92799007587</v>
       </c>
       <c r="X4" s="8" t="n">
-        <v>581582.2699642607</v>
+        <v>79292.60201187248</v>
       </c>
     </row>
     <row r="5">
@@ -6121,64 +6151,64 @@
         <v>20855.4</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>25463.43642165983</v>
+        <v>25477.34904841449</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>30640.99072919527</v>
+        <v>30265.99327979724</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>36872.72664334257</v>
+        <v>35470.78354283661</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>44373.58804934718</v>
+        <v>41003.46893112274</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>53402.4112735666</v>
+        <v>46743.46656024354</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>64270.9023777869</v>
+        <v>52539.49448363986</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>77354.45364974285</v>
+        <v>58213.96709501751</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>93105.17675129764</v>
+        <v>63570.25106717244</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>112067.6075949168</v>
+        <v>68402.5780346489</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>134897.6316157989</v>
+        <v>72508.07763207541</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>162385.2909912751</v>
+        <v>75700.07324267572</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>195482.2715133561</v>
+        <v>79037.48236602338</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>235335.0310510951</v>
+        <v>82527.19975087827</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>283324.7296480968</v>
+        <v>86176.46149101231</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>341115.3602895909</v>
+        <v>89992.86266475785</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>410711.7676959964</v>
+        <v>93984.3759224707</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>494529.5903603502</v>
+        <v>98159.37107456036</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>595479.580765109</v>
+        <v>102526.6357357372</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>717069.2651640109</v>
+        <v>107095.3970843074</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>863525.5154567866</v>
+        <v>111875.344798704</v>
       </c>
     </row>
     <row r="6">
@@ -6197,64 +6227,64 @@
         <v>18202</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>23122.05950777309</v>
+        <v>23130.56066322355</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>29092.80640481138</v>
+        <v>28865.07420448423</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>36292.31923643257</v>
+        <v>35423.21099504035</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>45001.95320047493</v>
+        <v>42869.92238216312</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>55557.27541727814</v>
+        <v>51257.77576486601</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>68360.5288266518</v>
+        <v>60628.08901178896</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>83895.37564947472</v>
+        <v>71013.50502228174</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>102744.4652561909</v>
+        <v>82442.24512363585</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>125610.464996896</v>
+        <v>94944.11657912612</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>153341.3102398511</v>
+        <v>108558.159296363</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>186960.5753224161</v>
+        <v>123341.6208012305</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>227704.0451994073</v>
+        <v>140121.0778155063</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>277063.7843605513</v>
+        <v>159146.9548781974</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>336841.2625843545</v>
+        <v>180704.7375389325</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>409211.4154787064</v>
+        <v>205118.887987066</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>496799.9026985973</v>
+        <v>232757.4258865683</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>602776.2917792804</v>
+        <v>264037.2211577346</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>730966.4570873907</v>
+        <v>299430.0613607529</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>885988.1613185176</v>
+        <v>339469.5718467511</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>1073414.605243922</v>
+        <v>384759.0825130233</v>
       </c>
     </row>
     <row r="7">
@@ -6273,64 +6303,64 @@
         <v>14383.9</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>12667.78110292276</v>
+        <v>12672.43859359015</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>15938.94795928385</v>
+        <v>15814.18131975239</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>19883.3134068341</v>
+        <v>19407.15889503546</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>24655.0222810362</v>
+        <v>23486.95592855667</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>30437.92026502977</v>
+        <v>28082.37229013855</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>37452.38243007485</v>
+        <v>33216.04461884841</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>45963.39067104919</v>
+        <v>38905.85683646183</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>56290.15853733661</v>
+        <v>45167.27043750712</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>68817.65330125947</v>
+        <v>52016.61579628835</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>84010.42958568553</v>
+        <v>59475.281535377</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>102429.2685634114</v>
+        <v>67574.63160513135</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>124751.2143053874</v>
+        <v>76767.51896065829</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>151793.7176248055</v>
+        <v>87191.14259333107</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>184543.7418503422</v>
+        <v>99001.91021629171</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>224192.8593929429</v>
+        <v>112377.5835029558</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>272179.5788659517</v>
+        <v>127519.7877688876</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>330240.3973021708</v>
+        <v>144656.9117048486</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>400471.3796731276</v>
+        <v>164047.4314875624</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>485402.4393281628</v>
+        <v>185983.7020924492</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>588086.9412752348</v>
+        <v>210796.267218231</v>
       </c>
     </row>
     <row r="8">
@@ -6349,64 +6379,64 @@
         <v>6.980260342615533</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>6.147457230769553</v>
+        <v>6.149717431229907</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>7.73489848672487</v>
+        <v>7.674351373215817</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>9.64903149031346</v>
+        <v>9.417961859986118</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>11.96466009042189</v>
+        <v>11.39781749295135</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>14.77100144868089</v>
+        <v>13.62789435573241</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>18.17499981320242</v>
+        <v>16.11917762161136</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>22.30524635969865</v>
+        <v>18.88034605155986</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>27.31664995708479</v>
+        <v>21.91890284409109</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>33.39602862997145</v>
+        <v>25.24277285019364</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>40.76882278123843</v>
+        <v>28.86233560211667</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>49.70716991054557</v>
+        <v>32.79281148785466</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>60.53962791099961</v>
+        <v>37.25396229131661</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>73.66289166322137</v>
+        <v>42.31236833345371</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>89.55591756865817</v>
+        <v>48.04393159893802</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>108.7969553124076</v>
+        <v>54.53491678367119</v>
       </c>
       <c r="T8" s="9" t="n">
-        <v>132.0840884897559</v>
+        <v>61.88316920041958</v>
       </c>
       <c r="U8" s="9" t="n">
-        <v>160.2600093728363</v>
+        <v>70.19952196960431</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>194.3419023967672</v>
+        <v>79.6094091533291</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>235.5574911846729</v>
+        <v>90.2547056145235</v>
       </c>
       <c r="X8" s="9" t="n">
-        <v>285.3885214853823</v>
+        <v>102.2958185495453</v>
       </c>
     </row>
   </sheetData>

--- a/engine/tmgh_study/TMGH_Valuation_Model_01092026.xlsx
+++ b/engine/tmgh_study/TMGH_Valuation_Model_01092026.xlsx
@@ -711,61 +711,61 @@
         <v>94007.06392117839</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>115942.9837642265</v>
+        <v>116623.4857926842</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>142349.2808961654</v>
+        <v>144709.4940935237</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>174040.8523455015</v>
+        <v>178544.4221690894</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>211880.0991718504</v>
+        <v>219058.7784506761</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>256776.0908634245</v>
+        <v>267231.7339009733</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>309683.3345392122</v>
+        <v>324089.062132737</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>371601.4510400648</v>
+        <v>390702.2200906162</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>443577.1399989407</v>
+        <v>468190.092845889</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>526709.8119975199</v>
+        <v>557724.9138541074</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>622162.1578588361</v>
+        <v>660543.741193012</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>731523.3703117218</v>
+        <v>778365.9976042513</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>856607.5325377719</v>
+        <v>913153.078190444</v>
       </c>
       <c r="P2" s="8" t="n">
-        <v>999478.812608933</v>
+        <v>1067135.765921361</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>1162480.945937615</v>
+        <v>1242846.2231769</v>
       </c>
       <c r="R2" s="8" t="n">
-        <v>1348271.307092299</v>
+        <v>1443154.897999628</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>1559859.974991126</v>
+        <v>1671312.791223556</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>1800654.295541997</v>
+        <v>1930999.636162403</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>2074509.546888571</v>
+        <v>2226378.649799319</v>
       </c>
       <c r="V2" s="8" t="n">
-        <v>2385786.417662771</v>
+        <v>2562158.626628032</v>
       </c>
     </row>
     <row r="3">
@@ -851,61 +851,61 @@
         <v>96401.92291199999</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>98005.10601417215</v>
+        <v>98458.43356617216</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>100067.7869536358</v>
+        <v>101574.6477364838</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>102615.6947613896</v>
+        <v>105324.4102968592</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>105663.3517812658</v>
+        <v>109725.4112554796</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>109211.3392928265</v>
+        <v>114776.80440154</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>113243.9788584783</v>
+        <v>120456.2323702893</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>117727.6898441762</v>
+        <v>126717.7648088749</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>122610.2643199192</v>
+        <v>133491.061411713</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>127821.2508016575</v>
+        <v>140682.003124515</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>133273.5590691119</v>
+        <v>148174.9281521069</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>138978.6703290248</v>
+        <v>155983.9666025561</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>144948.638250117</v>
+        <v>164123.9243326794</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>151196.1187203492</v>
+        <v>172610.3168688069</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>157734.4012117833</v>
+        <v>181459.4051013011</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>164577.4418427168</v>
+        <v>190688.2328491556</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>171739.8982318908</v>
+        <v>200314.6663963912</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>179237.1662450048</v>
+        <v>210357.4361076758</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>187085.4187395119</v>
+        <v>220836.1802366211</v>
       </c>
       <c r="V4" s="8" t="n">
-        <v>195301.6464197505</v>
+        <v>231771.4910465964</v>
       </c>
     </row>
     <row r="5">
@@ -991,61 +991,61 @@
         <v>496454.3553331784</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>526017.4606573987</v>
+        <v>527151.2902378563</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>566209.8125897233</v>
+        <v>570076.8865699295</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>616856.1849627667</v>
+        <v>624068.4703218243</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>677896.662830884</v>
+        <v>689137.4015839236</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>749322.6935687414</v>
+        <v>765343.8017150038</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>831135.224929656</v>
+        <v>852753.2060349918</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>923324.8395354013</v>
+        <v>951415.6835506514</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1025873.878189574</v>
+        <v>1061367.628128316</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>1138780.052677968</v>
+        <v>1182655.906857413</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>1262100.110191826</v>
+        <v>1315383.062608997</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>1398131.243477632</v>
+        <v>1461979.167043692</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>1549228.368120088</v>
+        <v>1624949.199855323</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>1717871.537341149</v>
+        <v>1806942.688802035</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>1906727.108991524</v>
+        <v>2010817.390120327</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>2118705.600943165</v>
+        <v>2239699.982856933</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>2357018.615080745</v>
+        <v>2497046.199477675</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>2625236.816145979</v>
+        <v>2786702.426629056</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>2927350.682281625</v>
+        <v>3112970.546689482</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>3267835.57149236</v>
+        <v>3480677.625084466</v>
       </c>
     </row>
     <row r="7">
@@ -1268,61 +1268,61 @@
         <v>100541.6070155131</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>111611.5339393398</v>
+        <v>112131.8898268824</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>125196.5451658646</v>
+        <v>126971.286932922</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>141637.4143158543</v>
+        <v>144947.3960043798</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>161295.0749189513</v>
+        <v>166453.8612932777</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>184546.3061521451</v>
+        <v>191898.9789810728</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>211780.4059376684</v>
+        <v>221701.6885879298</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>243397.4952439234</v>
+        <v>256289.4115612576</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>279809.1263013253</v>
+        <v>296098.5070600605</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>321441.8233760892</v>
+        <v>341578.0585182544</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>368744.0654996811</v>
+        <v>393197.5622806872</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>422481.3287721419</v>
+        <v>451783.4774438707</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>483515.1285874736</v>
+        <v>518266.1893131545</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>552816.4657388779</v>
+        <v>593694.4767484063</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>631480.7741909469</v>
+        <v>679251.6134377779</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>720744.6256291682</v>
+        <v>776273.3753403926</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>822004.4638225622</v>
+        <v>886268.2466830434</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>936837.665863856</v>
+        <v>1010940.143430747</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>1067026.25732857</v>
+        <v>1152214.005958761</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>1214583.644381332</v>
+        <v>1312264.651838045</v>
       </c>
     </row>
     <row r="11">
@@ -1338,61 +1338,61 @@
         <v>86110.92206963341</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>99161.81495436524</v>
+        <v>99775.28864728022</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>115177.8670543701</v>
+        <v>117270.1992675189</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>134560.8335079766</v>
+        <v>138463.1371785086</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>157736.2369827041</v>
+        <v>163818.1893614172</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>185148.2813756446</v>
+        <v>193816.7166929793</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>217255.9295614645</v>
+        <v>228952.6280165389</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>254530.9042475933</v>
+        <v>269729.8319455092</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>297458.405030431</v>
+        <v>316662.774210438</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>346541.282791417</v>
+        <v>370280.9018286967</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>402308.2719875161</v>
+        <v>431137.7276236807</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>465661.8308423641</v>
+        <v>500207.605736696</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>537617.6431272305</v>
+        <v>578587.4141367843</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>619320.4704498713</v>
+        <v>667513.610901229</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>712061.7749339815</v>
+        <v>768381.2168159535</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>817299.4130516622</v>
+        <v>882765.0452542058</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>936679.7225045481</v>
+        <v>1012443.524040998</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>1072062.352377739</v>
+        <v>1159425.485293925</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>1225548.22213204</v>
+        <v>1325980.337909708</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>1399511.037426833</v>
+        <v>1514672.083562228</v>
       </c>
     </row>
     <row r="12">
@@ -1408,61 +1408,61 @@
         <v>186652.5290851465</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>210773.348893705</v>
+        <v>211907.1784741626</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>240374.4122202347</v>
+        <v>244241.4862004409</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>276198.2478238308</v>
+        <v>283410.5331828883</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>319031.3119016553</v>
+        <v>330272.0506546948</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>369694.5875277898</v>
+        <v>385715.6956740521</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>429036.335499133</v>
+        <v>450654.3166044687</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>497928.3994915166</v>
+        <v>526019.2435067667</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>577267.5313317563</v>
+        <v>612761.2812704984</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>667983.1061675062</v>
+        <v>711858.9603469511</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>771052.3374871972</v>
+        <v>824335.2899043679</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>888143.1596145059</v>
+        <v>951991.0831805668</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>1021132.771714704</v>
+        <v>1096853.603449939</v>
       </c>
       <c r="P12" s="8" t="n">
-        <v>1172136.936188749</v>
+        <v>1261208.087649635</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>1343542.549124928</v>
+        <v>1447632.830253731</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>1538044.038680831</v>
+        <v>1659038.420594598</v>
       </c>
       <c r="S12" s="8" t="n">
-        <v>1758684.186327111</v>
+        <v>1898711.770724041</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>2008900.018241595</v>
+        <v>2170365.628724672</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>2292574.479460611</v>
+        <v>2478194.343868469</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>2614094.681808165</v>
+        <v>2826936.735400273</v>
       </c>
     </row>
     <row r="13">
@@ -1478,13 +1478,13 @@
         <v>0</v>
       </c>
       <c r="E13" s="9" t="n">
+        <v>1.164153218269348e-10</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>5.820766091346741e-11</v>
+      </c>
+      <c r="G13" s="9" t="n">
         <v>0</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>-5.820766091346741e-11</v>
       </c>
       <c r="H13" s="9" t="n">
         <v>-5.820766091346741e-11</v>
@@ -1496,40 +1496,40 @@
         <v>-2.328306436538696e-10</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>-1.164153218269348e-10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
         <v>-1.164153218269348e-10</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>-3.492459654808044e-10</v>
+        <v>1.164153218269348e-10</v>
       </c>
       <c r="N13" s="9" t="n">
-        <v>3.492459654808044e-10</v>
+        <v>1.164153218269348e-10</v>
       </c>
       <c r="O13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
+        <v>-2.328306436538696e-10</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>-4.656612873077393e-10</v>
+      </c>
+      <c r="R13" s="9" t="n">
+        <v>-6.984919309616089e-10</v>
+      </c>
+      <c r="S13" s="9" t="n">
+        <v>-4.656612873077393e-10</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>-9.313225746154785e-10</v>
+      </c>
+      <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="9" t="n">
-        <v>-6.984919309616089e-10</v>
-      </c>
-      <c r="R13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="9" t="n">
-        <v>-4.656612873077393e-10</v>
-      </c>
-      <c r="U13" s="9" t="n">
-        <v>4.656612873077393e-10</v>
-      </c>
       <c r="V13" s="9" t="n">
-        <v>4.656612873077393e-10</v>
+        <v>-9.313225746154785e-10</v>
       </c>
     </row>
   </sheetData>
@@ -1686,61 +1686,61 @@
         <v>24355.80881125544</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>29440.18041609003</v>
+        <v>30797.01966263739</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>35467.1870120833</v>
+        <v>38743.46529081929</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>42486.37947910043</v>
+        <v>46507.63315368938</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>50543.00387040331</v>
+        <v>55396.30671615424</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>59676.75281016456</v>
+        <v>65446.1039690499</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>69922.17636389198</v>
+        <v>76686.66768484155</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>81310.93636410446</v>
+        <v>89143.47503062025</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>93875.98045163541</v>
+        <v>102842.8234638758</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>107657.5661127697</v>
+        <v>117818.8917971868</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>122710.8986199299</v>
+        <v>134122.5808736047</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>139695.8621098253</v>
+        <v>152517.6433551638</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>158879.21696909</v>
+        <v>173291.4367166685</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>180558.7172652823</v>
+        <v>196764.9762598592</v>
       </c>
       <c r="P2" s="8" t="n">
-        <v>205068.0442956473</v>
+        <v>223298.2135859039</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>232782.1509308253</v>
+        <v>253295.7705329187</v>
       </c>
       <c r="R2" s="8" t="n">
-        <v>264123.1271015673</v>
+        <v>287213.2447122033</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>299566.6967890363</v>
+        <v>325564.203538761</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>339649.4604637559</v>
+        <v>368927.9880825881</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>384977.0036447825</v>
+        <v>417958.4557497925</v>
       </c>
     </row>
     <row r="3">
@@ -1750,64 +1750,64 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>-2320.413312000001</v>
+        <v>-2320.413312</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>-2760.006177116161</v>
+        <v>-3213.33372911616</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>-3238.74221163375</v>
+        <v>-4297.715373105748</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-3748.721251197387</v>
+        <v>-4968.658333213129</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>-4279.045357012842</v>
+        <v>-5664.893882182725</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>-4815.947732935925</v>
+        <v>-6368.098081126194</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>-5343.175637165725</v>
+        <v>-7056.74962156778</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>-5842.63873199966</v>
+        <v>-7707.007227029098</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>-6295.306753873037</v>
+        <v>-8293.909780544594</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>-6682.30965357735</v>
+        <v>-8792.834449742515</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>-6986.163277074304</v>
+        <v>-9181.109065086075</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>-7304.393968742251</v>
+        <v>-9587.137588274492</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>-7637.71196504048</v>
+        <v>-10011.76532935401</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>-7986.864129233592</v>
+        <v>-10455.87962811966</v>
       </c>
       <c r="P3" s="8" t="n">
-        <v>-8352.63591607839</v>
+        <v>-10920.41203491991</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>-8735.853445474848</v>
+        <v>-11406.34060907002</v>
       </c>
       <c r="R3" s="8" t="n">
-        <v>-9137.385691286567</v>
+        <v>-11914.69234142555</v>
       </c>
       <c r="S3" s="8" t="n">
-        <v>-9558.14679189671</v>
+        <v>-12446.54570804125</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>-9999.098489447146</v>
+        <v>-13003.03336223747</v>
       </c>
       <c r="U3" s="8" t="n">
-        <v>-10461.25270511278</v>
+        <v>-13585.34497281471</v>
       </c>
     </row>
     <row r="4">
@@ -1820,61 +1820,61 @@
         <v>-3801.731578077044</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>-4744.254395925717</v>
+        <v>-4967.264062015432</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>-5822.147668510639</v>
+        <v>-6359.741616874092</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-7046.086778567001</v>
+        <v>-7704.046744910468</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>-8424.711687041565</v>
+        <v>-9217.05655238482</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>-9964.813385654521</v>
+        <v>-10905.05043762649</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-11671.75705093855</v>
+        <v>-12772.58983151014</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>-13550.18113125213</v>
+        <v>-14823.30984571189</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>-15604.98473888651</v>
+        <v>-17061.04092805841</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>-17842.5844606131</v>
+        <v>-19491.23633922593</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>-20272.38948153941</v>
+        <v>-22122.64446961407</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>-23030.25568819749</v>
+        <v>-25108.24935565008</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>-26157.34277799932</v>
+        <v>-28492.59080112161</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>-29700.57306488751</v>
+        <v>-32326.40890082219</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>-33713.27505088675</v>
+        <v>-36667.34429544496</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>-38255.93633066627</v>
+        <v>-41580.75510112058</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>-43397.07351145458</v>
+        <v>-47140.65914685038</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>-49214.22944626872</v>
+        <v>-53430.81289187296</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>-55795.11062773475</v>
+        <v>-60545.9410834345</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>-63238.88016546929</v>
+        <v>-68593.13394826453</v>
       </c>
     </row>
     <row r="5">
@@ -2021,61 +2021,61 @@
         <v>13549.94762425544</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>15368.50845619121</v>
+        <v>16272.02015073857</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>17516.71144199443</v>
+        <v>19628.53874484749</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>19932.9488139974</v>
+        <v>22368.43236098009</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>22547.05552483774</v>
+        <v>25316.45652276265</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>25278.81883059182</v>
+        <v>28383.32435306889</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>28038.13576789546</v>
+        <v>31468.4284336229</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>30726.80990352692</v>
+        <v>34462.09229801692</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>33241.87791155231</v>
+        <v>37249.49869428568</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>35480.22888435654</v>
+        <v>39716.02208133149</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>37344.14360824008</v>
+        <v>41753.53928613197</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>39215.76279796343</v>
+        <v>43805.65500697248</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>41114.81173073265</v>
+        <v>45892.37088365551</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>43057.11471769403</v>
+        <v>48029.79863722069</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>45055.62155018427</v>
+        <v>50231.18695817297</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>47121.17999002004</v>
+        <v>52507.69445642918</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>49263.1179359743</v>
+        <v>54868.9723058354</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>51489.68299851498</v>
+        <v>57323.60431606862</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>53808.37529029918</v>
+        <v>59879.44024017821</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>56226.20029694128</v>
+        <v>62543.84918308332</v>
       </c>
     </row>
     <row r="8">
@@ -2088,61 +2088,61 @@
         <v>94007.06392117839</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>115942.9837642265</v>
+        <v>116623.4857926842</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>142349.2808961654</v>
+        <v>144709.4940935237</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>174040.8523455015</v>
+        <v>178544.4221690894</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>211880.0991718504</v>
+        <v>219058.7784506761</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>256776.0908634245</v>
+        <v>267231.7339009733</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>309683.3345392122</v>
+        <v>324089.062132737</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>371601.4510400648</v>
+        <v>390702.2200906162</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>443577.1399989407</v>
+        <v>468190.092845889</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>526709.8119975199</v>
+        <v>557724.9138541074</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>622162.1578588361</v>
+        <v>660543.741193012</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>731523.3703117218</v>
+        <v>778365.9976042513</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>856607.5325377719</v>
+        <v>913153.078190444</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>999478.812608933</v>
+        <v>1067135.765921361</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>1162480.945937615</v>
+        <v>1242846.2231769</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>1348271.307092299</v>
+        <v>1443154.897999628</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>1559859.974991126</v>
+        <v>1671312.791223556</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>1800654.295541997</v>
+        <v>1930999.636162403</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>2074509.546888571</v>
+        <v>2226378.649799319</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>2385786.417662771</v>
+        <v>2562158.626628032</v>
       </c>
     </row>
   </sheetData>
@@ -2299,61 +2299,61 @@
         <v>80546.09696</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>95682.499193344</v>
+        <v>100215.774713344</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>112133.5339768776</v>
+        <v>122723.2655915976</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>129620.0867262457</v>
+        <v>141819.4575464031</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>147760.8689123304</v>
+        <v>161619.3541640292</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>166077.5965088486</v>
+        <v>181599.0999907513</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>184008.9000458804</v>
+        <v>201144.639889901</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>200933.2742190017</v>
+        <v>219576.9591692961</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>216200.4207920049</v>
+        <v>236186.4510587204</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>229169.2873935428</v>
+        <v>250274.5353551944</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>239250.0898231309</v>
+        <v>261199.5477032487</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>249789.6974306805</v>
+        <v>272617.1336260029</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>260809.8412666213</v>
+        <v>284550.3749097565</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>272333.3270570734</v>
+        <v>297023.4820459341</v>
       </c>
       <c r="P2" s="8" t="n">
-        <v>284384.0906812427</v>
+        <v>310061.8518696578</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>296987.2566273254</v>
+        <v>323692.1282632772</v>
       </c>
       <c r="R2" s="8" t="n">
-        <v>310169.1995922365</v>
+        <v>337942.2660936264</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>323957.6093998931</v>
+        <v>352841.5985613385</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>338381.5594227531</v>
+        <v>368420.9081506563</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>353471.5787018567</v>
+        <v>384712.501378876</v>
       </c>
     </row>
     <row r="3">
@@ -2366,61 +2366,61 @@
         <v>0.3163076798254644</v>
       </c>
       <c r="C3" s="10" t="n">
-        <v>0.3163169182970363</v>
+        <v>0.3225320481559615</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>0.3163262789002158</v>
+        <v>0.3281813084766022</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.3163357622011241</v>
+        <v>0.3281530068117789</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>0.3163453687320789</v>
+        <v>0.3281243203819394</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>0.3163550989903721</v>
+        <v>0.3280952470266565</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>0.3163649534370487</v>
+        <v>0.3280657846805978</v>
       </c>
       <c r="I3" s="10" t="n">
-        <v>0.3163749324956791</v>
+        <v>0.3280359313773683</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.3163850365511335</v>
+        <v>0.3280056852533753</v>
       </c>
       <c r="K3" s="10" t="n">
-        <v>0.3163952659483569</v>
+        <v>0.3279750445517202</v>
       </c>
       <c r="L3" s="10" t="n">
-        <v>0.3164056209911482</v>
+        <v>0.3279440076261054</v>
       </c>
       <c r="M3" s="10" t="n">
-        <v>0.3164161019409424</v>
+        <v>0.327912572944757</v>
       </c>
       <c r="N3" s="10" t="n">
-        <v>0.316426709015601</v>
+        <v>0.3278807390943531</v>
       </c>
       <c r="O3" s="10" t="n">
-        <v>0.3164374423882104</v>
+        <v>0.3278485047839593</v>
       </c>
       <c r="P3" s="10" t="n">
-        <v>0.3164483021858915</v>
+        <v>0.3278158688489589</v>
       </c>
       <c r="Q3" s="10" t="n">
-        <v>0.3164592884886203</v>
+        <v>0.3277828302549782</v>
       </c>
       <c r="R3" s="10" t="n">
-        <v>0.3164704013280668</v>
+        <v>0.3277493881017979</v>
       </c>
       <c r="S3" s="10" t="n">
-        <v>0.3164816406864467</v>
+        <v>0.3277155416272459</v>
       </c>
       <c r="T3" s="10" t="n">
-        <v>0.3164930064953954</v>
+        <v>0.3276812902110643</v>
       </c>
       <c r="U3" s="10" t="n">
-        <v>0.3165044986348611</v>
+        <v>0.3276466333787461</v>
       </c>
     </row>
     <row r="4">
@@ -2433,61 +2433,61 @@
         <v>0.2346099989937993</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.2367157990725232</v>
+        <v>0.2434778321250171</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.2383273435270836</v>
+        <v>0.2510430544446013</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.2395607693625308</v>
+        <v>0.252047413386181</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.2405008193003875</v>
+        <v>0.2527932445424318</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>0.2412094604028764</v>
+        <v>0.2533337404023637</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>0.2417319264298251</v>
+        <v>0.2537074727078367</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>0.2421009599497582</v>
+        <v>0.2539420400434187</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>0.2423397795504088</v>
+        <v>0.2540566026942072</v>
       </c>
       <c r="K4" s="10" t="n">
-        <v>0.2424641272203436</v>
+        <v>0.2540636094505153</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>0.2424836333252141</v>
+        <v>0.2539699181381967</v>
       </c>
       <c r="M4" s="10" t="n">
-        <v>0.2425026923887784</v>
+        <v>0.2538793492519897</v>
       </c>
       <c r="N4" s="10" t="n">
-        <v>0.2425213333619918</v>
+        <v>0.2537917224201887</v>
       </c>
       <c r="O4" s="10" t="n">
-        <v>0.2425395836868875</v>
+        <v>0.2537068665140548</v>
       </c>
       <c r="P4" s="10" t="n">
-        <v>0.2425574693700679</v>
+        <v>0.2536246191889358</v>
       </c>
       <c r="Q4" s="10" t="n">
-        <v>0.2425750150524477</v>
+        <v>0.253544826448671</v>
       </c>
       <c r="R4" s="10" t="n">
-        <v>0.2425922440754454</v>
+        <v>0.2534673422321055</v>
       </c>
       <c r="S4" s="10" t="n">
-        <v>0.2426091785437974</v>
+        <v>0.2533920280205975</v>
       </c>
       <c r="T4" s="10" t="n">
-        <v>0.2426258393851708</v>
+        <v>0.2533187524654563</v>
       </c>
       <c r="U4" s="10" t="n">
-        <v>0.2426422464067382</v>
+        <v>0.2532473910343054</v>
       </c>
     </row>
     <row r="5">
@@ -2500,61 +2500,61 @@
         <v>23130.56066322355</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>28865.07420448423</v>
+        <v>30221.91345103159</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>35423.21099504035</v>
+        <v>38694.04934315235</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>42869.92238216312</v>
+        <v>46873.09372735789</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>51257.77576486601</v>
+        <v>56078.57402419132</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>60628.08901178896</v>
+        <v>66348.69545698373</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>71013.50502228174</v>
+        <v>77711.21076192675</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>82442.24512363585</v>
+        <v>90188.23674800989</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>94944.11657912612</v>
+        <v>103803.0786917901</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>108558.159296363</v>
+        <v>118588.9154156786</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>123341.6208012305</v>
+        <v>134598.9740270309</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>140121.0778155063</v>
+        <v>152764.0426318489</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>159146.9548781974</v>
+        <v>173355.1110704936</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>180704.7375389325</v>
+        <v>196680.8931005187</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>205118.887987066</v>
+        <v>223092.0868995411</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>232757.4258865683</v>
+        <v>252986.3454419876</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>264037.2211577346</v>
+        <v>286814.0092762934</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>299430.0613607529</v>
+        <v>325084.6708925036</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>339469.5718467511</v>
+        <v>368374.6562272313</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>384759.0825130233</v>
+        <v>417335.525480068</v>
       </c>
     </row>
     <row r="6">
@@ -2567,61 +2567,61 @@
         <v>12672.43859359015</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>15814.18131975239</v>
+        <v>16557.54687338477</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>19407.15889503546</v>
+        <v>21199.13872291364</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>23486.95592855667</v>
+        <v>25680.15581636823</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>28082.37229013855</v>
+        <v>30723.52184128273</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>33216.04461884841</v>
+        <v>36350.16812542162</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>38905.85683646183</v>
+        <v>42575.29943836714</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>45167.27043750712</v>
+        <v>49411.03281903962</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>52016.61579628835</v>
+        <v>56870.13642686138</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>59475.281535377</v>
+        <v>64970.78779741978</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>67574.63160513135</v>
+        <v>73742.14823204691</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>76767.51896065829</v>
+        <v>83694.16451883361</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>87191.14259333107</v>
+        <v>94975.30267040538</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>99001.91021629171</v>
+        <v>107754.696336074</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>112377.5835029558</v>
+        <v>122224.4809848165</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>127519.7877688876</v>
+        <v>138602.5170037353</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>144656.9117048486</v>
+        <v>157135.5304895013</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>164047.4314875624</v>
+        <v>178102.7096395766</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>185983.7020924492</v>
+        <v>201819.8036114484</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>210796.267218231</v>
+        <v>228643.7798275485</v>
       </c>
     </row>
     <row r="7">
@@ -2634,61 +2634,61 @@
         <v>6.149717431229907</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7.674351373215817</v>
+        <v>8.035093946098453</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>9.417961859986118</v>
+        <v>10.28757898241502</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>11.39781749295135</v>
+        <v>12.462139839486</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>13.62789435573241</v>
+        <v>14.90959900264796</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>16.11917762161136</v>
+        <v>17.64011408681149</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>18.88034605155986</v>
+        <v>20.66106370626989</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>21.91890284409109</v>
+        <v>23.97832805250432</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>25.24277285019364</v>
+        <v>27.59810329462493</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>28.86233560211667</v>
+        <v>31.52921067935806</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>32.79281148785466</v>
+        <v>35.78580168684663</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>37.25396229131661</v>
+        <v>40.61534476040255</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>42.31236833345371</v>
+        <v>46.08988791344057</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>48.04393159893802</v>
+        <v>52.2915088095215</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>54.53491678367119</v>
+        <v>59.3134475013787</v>
       </c>
       <c r="Q7" s="9" t="n">
-        <v>61.88316920041958</v>
+        <v>67.26142790396682</v>
       </c>
       <c r="R7" s="9" t="n">
-        <v>70.19952196960431</v>
+        <v>76.25518196676282</v>
       </c>
       <c r="S7" s="9" t="n">
-        <v>79.6094091533291</v>
+        <v>86.43019494083701</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>90.2547056145235</v>
+        <v>97.93969448504565</v>
       </c>
       <c r="U7" s="9" t="n">
-        <v>102.2958185495453</v>
+        <v>110.9569107763509</v>
       </c>
     </row>
     <row r="8">
@@ -3060,10 +3060,10 @@
         <v>0.22</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>70.16479609998046</v>
+        <v>76.86679522233983</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>97.0097244573295</v>
+        <v>103.7117235796888</v>
       </c>
       <c r="D2" s="10">
         <f>B2/'Summary'!$B$2-1</f>
@@ -3075,10 +3075,10 @@
         <v>0.25</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>63.76257054983443</v>
+        <v>69.73797463202921</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>87.29699363888786</v>
+        <v>93.2723977210826</v>
       </c>
       <c r="D3" s="10">
         <f>B3/'Summary'!$B$2-1</f>
@@ -3090,10 +3090,10 @@
         <v>0.2849</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>57.32583665473236</v>
+        <v>62.57295613738459</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>77.58016581124872</v>
+        <v>82.82728529390097</v>
       </c>
       <c r="D4" s="10">
         <f>B4/'Summary'!$B$2-1</f>
@@ -3105,10 +3105,10 @@
         <v>0.3157</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>52.41009407163257</v>
+        <v>57.10287328978551</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>70.19772724656579</v>
+        <v>74.89050646471871</v>
       </c>
       <c r="D5" s="10">
         <f>B5/'Summary'!$B$2-1</f>
@@ -3120,10 +3120,10 @@
         <v>0.3237</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>51.23655514421238</v>
+        <v>55.79727422175603</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>68.44086712244061</v>
+        <v>73.0015861999842</v>
       </c>
       <c r="D6" s="10">
         <f>B6/'Summary'!$B$2-1</f>
@@ -3135,10 +3135,10 @@
         <v>0.3579</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>46.64455562171646</v>
+        <v>50.68972727303409</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>61.58950989620313</v>
+        <v>65.63468154752078</v>
       </c>
       <c r="D7" s="10">
         <f>B7/'Summary'!$B$2-1</f>
@@ -3150,10 +3150,10 @@
         <v>0.4</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>41.81648289180088</v>
+        <v>45.32203314800572</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>54.43119936604813</v>
+        <v>57.93674962225298</v>
       </c>
       <c r="D8" s="10">
         <f>B8/'Summary'!$B$2-1</f>
@@ -3177,7 +3177,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>46.64029756780567</v>
+        <v>50.68499212889682</v>
       </c>
     </row>
     <row r="12">
@@ -3185,7 +3185,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>46.64029756780567</v>
+        <v>50.68499212889682</v>
       </c>
     </row>
     <row r="13">
@@ -3193,7 +3193,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>46.64029756780567</v>
+        <v>50.68499212889682</v>
       </c>
     </row>
     <row r="14">
@@ -3201,7 +3201,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>46.64029756780567</v>
+        <v>50.68499212889682</v>
       </c>
     </row>
     <row r="15">
@@ -3209,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>46.64029756780567</v>
+        <v>50.68499212889682</v>
       </c>
     </row>
     <row r="16">
@@ -3217,7 +3217,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>46.64029756780567</v>
+        <v>50.68499212889682</v>
       </c>
     </row>
   </sheetData>
@@ -3680,17 +3680,17 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>96360.51181116889</v>
+        <v>106030.9924788625</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>108001.6118111689</v>
+        <v>117672.0924788625</v>
       </c>
       <c r="D7" s="9">
         <f>C7/$B$3</f>
         <v/>
       </c>
       <c r="E7" s="9" t="n">
-        <v>48.82813681143778</v>
+        <v>51.39922425996588</v>
       </c>
       <c r="F7" s="10">
         <f>D7/$B$2-1</f>
@@ -3704,17 +3704,17 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>133015.9368125314</v>
+        <v>142686.417480225</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>144657.0368125314</v>
+        <v>154327.517480225</v>
       </c>
       <c r="D8" s="9">
         <f>C8/$B$3</f>
         <v/>
       </c>
       <c r="E8" s="9" t="n">
-        <v>58.57370235052318</v>
+        <v>61.14478979905127</v>
       </c>
       <c r="F8" s="10">
         <f>D8/$B$2-1</f>
@@ -3728,17 +3728,17 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>106490.7945082575</v>
+        <v>117303.6516572099</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>118131.8945082575</v>
+        <v>128944.7516572099</v>
       </c>
       <c r="D9" s="9">
         <f>C9/$B$3</f>
         <v/>
       </c>
       <c r="E9" s="9" t="n">
-        <v>51.52147167115555</v>
+        <v>54.39628237123518</v>
       </c>
       <c r="F9" s="10">
         <f>D9/$B$2-1</f>
@@ -3752,17 +3752,17 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>148229.5677143865</v>
+        <v>159042.4248633388</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>159870.6677143865</v>
+        <v>170683.5248633388</v>
       </c>
       <c r="D10" s="9">
         <f>C10/$B$3</f>
         <v/>
       </c>
       <c r="E10" s="9" t="n">
-        <v>62.61854529085117</v>
+        <v>65.49335599093081</v>
       </c>
       <c r="F10" s="10">
         <f>D10/$B$2-1</f>
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.1558113694332027</v>
+        <v>0.165447241670604</v>
       </c>
     </row>
     <row r="16">
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.2177365969170268</v>
+        <v>0.2364657157943358</v>
       </c>
     </row>
     <row r="17">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>52.4113326611044</v>
+        <v>57.10425132007254</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>77.58249722218574</v>
+        <v>82.82979162406552</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>85360.87492776931</v>
+        <v>93795.42211005262</v>
       </c>
     </row>
     <row r="3">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>10999.63688339958</v>
+        <v>12235.57036880988</v>
       </c>
     </row>
     <row r="5">
@@ -5070,61 +5070,61 @@
         <v>80546.09696</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>95682.499193344</v>
+        <v>100215.774713344</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>112133.5339768776</v>
+        <v>122723.2655915976</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>129620.0867262457</v>
+        <v>141819.4575464031</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>147760.8689123304</v>
+        <v>161619.3541640292</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>166077.5965088486</v>
+        <v>181599.0999907513</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>184008.9000458804</v>
+        <v>201144.639889901</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>200933.2742190017</v>
+        <v>219576.9591692961</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>216200.4207920049</v>
+        <v>236186.4510587204</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>229169.2873935428</v>
+        <v>250274.5353551944</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>239250.0898231309</v>
+        <v>261199.5477032487</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>249789.6974306805</v>
+        <v>272617.1336260029</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>260809.8412666213</v>
+        <v>284550.3749097565</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>272333.3270570734</v>
+        <v>297023.4820459341</v>
       </c>
       <c r="P2" s="8" t="n">
-        <v>284384.0906812427</v>
+        <v>310061.8518696578</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>296987.2566273254</v>
+        <v>323692.1282632772</v>
       </c>
       <c r="R2" s="8" t="n">
-        <v>310169.1995922365</v>
+        <v>337942.2660936264</v>
       </c>
       <c r="S2" s="8" t="n">
-        <v>323957.6093998931</v>
+        <v>352841.5985613385</v>
       </c>
       <c r="T2" s="8" t="n">
-        <v>338381.5594227531</v>
+        <v>368420.9081506563</v>
       </c>
       <c r="U2" s="8" t="n">
-        <v>353471.5787018567</v>
+        <v>384712.501378876</v>
       </c>
     </row>
     <row r="3">
@@ -5137,61 +5137,61 @@
         <v>55068.7479115855</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>65416.50591354676</v>
+        <v>67892.97563751273</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>76662.75043404101</v>
+        <v>82447.78370922552</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>88616.61779512296</v>
+        <v>95280.97612813552</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>101017.4023520869</v>
+        <v>108588.1134183892</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>113538.1020252087</v>
+        <v>122017.2984194673</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>125794.9329508629</v>
+        <v>135155.9657701243</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>137363.0231518293</v>
+        <v>147547.8268591857</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>147797.842757356</v>
+        <v>158715.9523316421</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>156661.2097614674</v>
+        <v>168190.7334719135</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>163550.0165804552</v>
+        <v>175540.7212393192</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>170752.2150646572</v>
+        <v>183222.5479098757</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>178282.641515743</v>
+        <v>191251.7876747703</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>186156.8655660611</v>
+        <v>199644.7775714494</v>
       </c>
       <c r="P3" s="8" t="n">
-        <v>194391.2280164848</v>
+        <v>208418.6565020887</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>203002.8807048547</v>
+        <v>217591.4063298828</v>
       </c>
       <c r="R3" s="8" t="n">
-        <v>212009.8285176762</v>
+        <v>227181.8951677054</v>
       </c>
       <c r="S3" s="8" t="n">
-        <v>221430.9736641559</v>
+        <v>237209.9229801862</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>231286.1623384457</v>
+        <v>247696.2696271172</v>
       </c>
       <c r="U3" s="8" t="n">
-        <v>241596.2339031527</v>
+        <v>258662.7454833711</v>
       </c>
     </row>
     <row r="4">
@@ -5204,61 +5204,61 @@
         <v>25477.34904841449</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>30265.99327979724</v>
+        <v>32322.79907583125</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>35470.78354283661</v>
+        <v>40275.48188237207</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>41003.46893112274</v>
+        <v>46538.48141826762</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>46743.46656024354</v>
+        <v>53031.24074564007</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>52539.49448363986</v>
+        <v>59581.80157128404</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>58213.96709501751</v>
+        <v>65988.67411977664</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>63570.25106717244</v>
+        <v>72029.13231011041</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>68402.5780346489</v>
+        <v>77470.49872707837</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>72508.07763207541</v>
+        <v>82083.80188328095</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>75700.07324267572</v>
+        <v>85658.82646392946</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>79037.48236602338</v>
+        <v>89394.58571612724</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>82527.19975087827</v>
+        <v>93298.58723498625</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>86176.46149101231</v>
+        <v>97378.70447448466</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>89992.86266475785</v>
+        <v>101643.1953675691</v>
       </c>
       <c r="Q4" s="8" t="n">
-        <v>93984.3759224707</v>
+        <v>106100.7219333944</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>98159.37107456036</v>
+        <v>110760.370925921</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>102526.6357357372</v>
+        <v>115631.6755811523</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>107095.3970843074</v>
+        <v>120724.6385235391</v>
       </c>
       <c r="U4" s="8" t="n">
-        <v>111875.344798704</v>
+        <v>126049.755895505</v>
       </c>
     </row>
     <row r="5">
@@ -5271,61 +5271,61 @@
         <v>5437.738921674436</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>6459.610951044766</v>
+        <v>6765.656428953144</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>7570.234997653327</v>
+        <v>8285.157234047301</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>8750.76778670173</v>
+        <v>9574.35820302759</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>9975.468189154244</v>
+        <v>10911.06690210042</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>11212.04682335868</v>
+        <v>12259.9173818584</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>12422.60513517979</v>
+        <v>13579.45423176347</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>13565.18474660238</v>
+        <v>14823.83656368543</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>14595.8834430787</v>
+        <v>15945.15819099173</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>15471.42320665294</v>
+        <v>16896.2573404491</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>16151.98717935921</v>
+        <v>17633.81467850722</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>16863.52549927569</v>
+        <v>18404.62609838962</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>17607.50524901955</v>
+        <v>19210.24987209804</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>18385.46606352335</v>
+        <v>20052.32047152498</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>19199.02387536353</v>
+        <v>20932.55245968522</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>20049.8748611707</v>
+        <v>21852.74458886526</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>20939.79960028235</v>
+        <v>22814.78411708469</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>21870.66745743409</v>
+        <v>23820.65135490852</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>22844.44120195883</v>
+        <v>24872.42445533224</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>23863.18187667519</v>
+        <v>25972.28446018353</v>
       </c>
     </row>
     <row r="6">
@@ -5341,58 +5341,58 @@
         <v>1156.823074944</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1176.061272170066</v>
+        <v>1181.501202794066</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1200.81344344363</v>
+        <v>1218.895772837806</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1231.388337136675</v>
+        <v>1263.89292356231</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1267.960221375189</v>
+        <v>1316.704935065755</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1310.536071513918</v>
+        <v>1377.32165281848</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>1358.92774630174</v>
+        <v>1445.474788443472</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1412.732278130115</v>
+        <v>1520.613177706499</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1471.32317183903</v>
+        <v>1601.892736940556</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>1533.85500961989</v>
+        <v>1688.18403749418</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>1599.282708829343</v>
+        <v>1778.099137825282</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>1667.744043948298</v>
+        <v>1871.807599230673</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>1739.383659001403</v>
+        <v>1969.487091992153</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>1814.35342464419</v>
+        <v>2071.323802425683</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>1892.8128145414</v>
+        <v>2177.512861215614</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>1974.929302112602</v>
+        <v>2288.258794189867</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>2060.878778782689</v>
+        <v>2403.775996756695</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>2150.845994940057</v>
+        <v>2524.289233292109</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>2245.025024874142</v>
+        <v>2650.034162839454</v>
       </c>
     </row>
     <row r="7">
@@ -5405,61 +5405,61 @@
         <v>18896.91972674006</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>22649.55925380848</v>
+        <v>24400.31957193411</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>26724.48727301322</v>
+        <v>30808.82344553071</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>31051.88770097738</v>
+        <v>35745.22744240223</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>35536.61003395262</v>
+        <v>40856.28091997735</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>40059.48743890599</v>
+        <v>46005.17925435989</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>44480.8258883238</v>
+        <v>51031.89823519469</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>48646.13857426833</v>
+        <v>55759.82095798151</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>52393.96231344009</v>
+        <v>60004.72735838014</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>55565.33125358343</v>
+        <v>63585.65180589128</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>58014.23105369662</v>
+        <v>66336.82774792807</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>60574.67415791834</v>
+        <v>69211.86047991234</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>63251.95045791042</v>
+        <v>72216.52976365754</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>66051.61176848755</v>
+        <v>75356.89691096754</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>68979.48536475014</v>
+        <v>78639.31910545817</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>72041.68824675861</v>
+        <v>82070.46448331357</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>75244.6421721654</v>
+        <v>85657.32801464645</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>78595.08949952044</v>
+        <v>89407.2482294871</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>82100.1098874085</v>
+        <v>93327.92483491471</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>85767.13789715467</v>
+        <v>97427.43727248197</v>
       </c>
     </row>
     <row r="8">
@@ -5472,61 +5472,61 @@
         <v>13549.94762425544</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>15368.50845619121</v>
+        <v>16272.02015073857</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>17516.71144199443</v>
+        <v>19628.53874484749</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>19932.9488139974</v>
+        <v>22368.43236098009</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>22547.05552483774</v>
+        <v>25316.45652276265</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>25278.81883059182</v>
+        <v>28383.32435306889</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>28038.13576789546</v>
+        <v>31468.4284336229</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>30726.80990352692</v>
+        <v>34462.09229801692</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>33241.87791155231</v>
+        <v>37249.49869428568</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>35480.22888435654</v>
+        <v>39716.02208133149</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>37344.14360824008</v>
+        <v>41753.53928613197</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>39215.76279796343</v>
+        <v>43805.65500697248</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>41114.81173073265</v>
+        <v>45892.37088365551</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>43057.11471769403</v>
+        <v>48029.79863722069</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>45055.62155018427</v>
+        <v>50231.18695817297</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>47121.17999002004</v>
+        <v>52507.69445642918</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>49263.1179359743</v>
+        <v>54868.9723058354</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>51489.68299851498</v>
+        <v>57323.60431606862</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>53808.37529029918</v>
+        <v>59879.44024017821</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>56226.20029694128</v>
+        <v>62543.84918308332</v>
       </c>
     </row>
     <row r="9">
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>10999.63688339958</v>
+        <v>12235.57036880988</v>
       </c>
     </row>
     <row r="15">
@@ -6002,61 +6002,61 @@
         <v>17867.64</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>21155.28576000001</v>
+        <v>25688.56127999999</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>24709.37376768001</v>
+        <v>35299.10538239999</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>28465.19858036738</v>
+        <v>40664.56940052479</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>32336.46558729735</v>
+        <v>46194.95083899617</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>36216.84145777303</v>
+        <v>51738.34493967571</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>39983.39296938143</v>
+        <v>57119.13281340199</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>43501.931550687</v>
+        <v>62145.61650098137</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>46634.07062233646</v>
+        <v>66620.10088905203</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>49245.57857718731</v>
+        <v>70350.82653883896</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>51215.4017202748</v>
+        <v>73164.85960039252</v>
       </c>
       <c r="P3" s="8" t="n">
-        <v>53264.0177890858</v>
+        <v>76091.45398440822</v>
       </c>
       <c r="Q3" s="8" t="n">
-        <v>55394.57850064923</v>
+        <v>79135.11214378454</v>
       </c>
       <c r="R3" s="8" t="n">
-        <v>57610.3616406752</v>
+        <v>82300.51662953592</v>
       </c>
       <c r="S3" s="8" t="n">
-        <v>59914.77610630221</v>
+        <v>85592.53729471736</v>
       </c>
       <c r="T3" s="8" t="n">
-        <v>62311.3671505543</v>
+        <v>89016.23878650606</v>
       </c>
       <c r="U3" s="8" t="n">
-        <v>64803.82183657648</v>
+        <v>92576.8883379663</v>
       </c>
       <c r="V3" s="8" t="n">
-        <v>67395.97471003953</v>
+        <v>96279.96387148496</v>
       </c>
       <c r="W3" s="8" t="n">
-        <v>70091.81369844111</v>
+        <v>100131.1624263444</v>
       </c>
       <c r="X3" s="8" t="n">
-        <v>72895.48624637876</v>
+        <v>104136.4089233981</v>
       </c>
     </row>
     <row r="4">
@@ -6154,61 +6154,61 @@
         <v>25477.34904841449</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>30265.99327979724</v>
+        <v>32322.79907583125</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>35470.78354283661</v>
+        <v>40275.48188237207</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>41003.46893112274</v>
+        <v>46538.48141826762</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>46743.46656024354</v>
+        <v>53031.24074564007</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>52539.49448363986</v>
+        <v>59581.80157128404</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>58213.96709501751</v>
+        <v>65988.67411977664</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>63570.25106717244</v>
+        <v>72029.13231011041</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>68402.5780346489</v>
+        <v>77470.49872707837</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>72508.07763207541</v>
+        <v>82083.80188328095</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>75700.07324267572</v>
+        <v>85658.82646392946</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>79037.48236602338</v>
+        <v>89394.58571612724</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>82527.19975087827</v>
+        <v>93298.58723498625</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>86176.46149101231</v>
+        <v>97378.70447448466</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>89992.86266475785</v>
+        <v>101643.1953675691</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>93984.3759224707</v>
+        <v>106100.7219333944</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>98159.37107456036</v>
+        <v>110760.370925921</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>102526.6357357372</v>
+        <v>115631.6755811523</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>107095.3970843074</v>
+        <v>120724.6385235391</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>111875.344798704</v>
+        <v>126049.755895505</v>
       </c>
     </row>
     <row r="6">
@@ -6230,61 +6230,61 @@
         <v>23130.56066322355</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>28865.07420448423</v>
+        <v>30221.91345103159</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>35423.21099504035</v>
+        <v>38694.04934315235</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>42869.92238216312</v>
+        <v>46873.09372735789</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>51257.77576486601</v>
+        <v>56078.57402419132</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>60628.08901178896</v>
+        <v>66348.69545698373</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>71013.50502228174</v>
+        <v>77711.21076192675</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>82442.24512363585</v>
+        <v>90188.23674800989</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>94944.11657912612</v>
+        <v>103803.0786917901</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>108558.159296363</v>
+        <v>118588.9154156786</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>123341.6208012305</v>
+        <v>134598.9740270309</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>140121.0778155063</v>
+        <v>152764.0426318489</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>159146.9548781974</v>
+        <v>173355.1110704936</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>180704.7375389325</v>
+        <v>196680.8931005187</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>205118.887987066</v>
+        <v>223092.0868995411</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>232757.4258865683</v>
+        <v>252986.3454419876</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>264037.2211577346</v>
+        <v>286814.0092762934</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>299430.0613607529</v>
+        <v>325084.6708925036</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>339469.5718467511</v>
+        <v>368374.6562272313</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>384759.0825130233</v>
+        <v>417335.525480068</v>
       </c>
     </row>
     <row r="7">
@@ -6306,61 +6306,61 @@
         <v>12672.43859359015</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>15814.18131975239</v>
+        <v>16557.54687338477</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>19407.15889503546</v>
+        <v>21199.13872291364</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>23486.95592855667</v>
+        <v>25680.15581636823</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>28082.37229013855</v>
+        <v>30723.52184128273</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>33216.04461884841</v>
+        <v>36350.16812542162</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>38905.85683646183</v>
+        <v>42575.29943836714</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>45167.27043750712</v>
+        <v>49411.03281903962</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>52016.61579628835</v>
+        <v>56870.13642686138</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>59475.281535377</v>
+        <v>64970.78779741978</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>67574.63160513135</v>
+        <v>73742.14823204691</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>76767.51896065829</v>
+        <v>83694.16451883361</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>87191.14259333107</v>
+        <v>94975.30267040538</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>99001.91021629171</v>
+        <v>107754.696336074</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>112377.5835029558</v>
+        <v>122224.4809848165</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>127519.7877688876</v>
+        <v>138602.5170037353</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>144656.9117048486</v>
+        <v>157135.5304895013</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>164047.4314875624</v>
+        <v>178102.7096395766</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>185983.7020924492</v>
+        <v>201819.8036114484</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>210796.267218231</v>
+        <v>228643.7798275485</v>
       </c>
     </row>
     <row r="8">
@@ -6382,61 +6382,61 @@
         <v>6.149717431229907</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>7.674351373215817</v>
+        <v>8.035093946098453</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>9.417961859986118</v>
+        <v>10.28757898241502</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>11.39781749295135</v>
+        <v>12.462139839486</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>13.62789435573241</v>
+        <v>14.90959900264796</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>16.11917762161136</v>
+        <v>17.64011408681149</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>18.88034605155986</v>
+        <v>20.66106370626989</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>21.91890284409109</v>
+        <v>23.97832805250432</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>25.24277285019364</v>
+        <v>27.59810329462493</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>28.86233560211667</v>
+        <v>31.52921067935806</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>32.79281148785466</v>
+        <v>35.78580168684663</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>37.25396229131661</v>
+        <v>40.61534476040255</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>42.31236833345371</v>
+        <v>46.08988791344057</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>48.04393159893802</v>
+        <v>52.2915088095215</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>54.53491678367119</v>
+        <v>59.3134475013787</v>
       </c>
       <c r="T8" s="9" t="n">
-        <v>61.88316920041958</v>
+        <v>67.26142790396682</v>
       </c>
       <c r="U8" s="9" t="n">
-        <v>70.19952196960431</v>
+        <v>76.25518196676282</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>79.6094091533291</v>
+        <v>86.43019494083701</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>90.2547056145235</v>
+        <v>97.93969448504565</v>
       </c>
       <c r="X8" s="9" t="n">
-        <v>102.2958185495453</v>
+        <v>110.9569107763509</v>
       </c>
     </row>
   </sheetData>
